--- a/Расчёт2.xlsx
+++ b/Расчёт2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Professional\Downloads\интститут\курсач детмаш\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5AA4FCC0-20CE-417A-8E8A-3337CB8581BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{30A501CD-B8BA-43E8-AF90-288A69021433}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{7E097F76-7D13-4899-AD2E-10ADA644057F}"/>
   </bookViews>
@@ -586,7 +586,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="54">
+  <cellXfs count="60">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" quotePrefix="1" applyBorder="1"/>
@@ -628,12 +628,15 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="10" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
@@ -642,13 +645,25 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -657,7 +672,16 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
@@ -669,22 +693,8 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -999,30 +1009,30 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2958CC72-8A25-4698-8914-B1180636D74D}">
-  <dimension ref="A1:AF69"/>
+  <dimension ref="A1:AK69"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="28" width="6.77734375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A1" s="41" t="s">
+    <row r="1" spans="1:37" x14ac:dyDescent="0.3">
+      <c r="A1" s="42" t="s">
         <v>10</v>
       </c>
-      <c r="B1" s="39"/>
-      <c r="C1" s="39"/>
-      <c r="D1" s="39"/>
-      <c r="E1" s="39"/>
-      <c r="F1" s="39"/>
+      <c r="B1" s="43"/>
+      <c r="C1" s="43"/>
+      <c r="D1" s="43"/>
+      <c r="E1" s="43"/>
+      <c r="F1" s="43"/>
       <c r="G1" s="6"/>
     </row>
-    <row r="2" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A2" s="41" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="39"/>
-      <c r="C2" s="39"/>
-      <c r="D2" s="39"/>
+    <row r="2" spans="1:37" x14ac:dyDescent="0.3">
+      <c r="A2" s="42" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="43"/>
+      <c r="C2" s="43"/>
+      <c r="D2" s="43"/>
       <c r="E2" s="20">
         <v>4</v>
       </c>
@@ -1030,22 +1040,22 @@
         <v>4</v>
       </c>
       <c r="G2" s="6"/>
-      <c r="I2" s="41" t="s">
+      <c r="I2" s="42" t="s">
         <v>61</v>
       </c>
-      <c r="J2" s="39"/>
-      <c r="K2" s="39"/>
-      <c r="L2" s="39"/>
-      <c r="M2" s="39">
+      <c r="J2" s="43"/>
+      <c r="K2" s="43"/>
+      <c r="L2" s="43"/>
+      <c r="M2" s="43">
         <f>E2*E3</f>
         <v>6.4</v>
       </c>
-      <c r="N2" s="40"/>
-      <c r="Q2" s="41" t="s">
+      <c r="N2" s="44"/>
+      <c r="Q2" s="42" t="s">
         <v>29</v>
       </c>
-      <c r="R2" s="39"/>
-      <c r="S2" s="39"/>
+      <c r="R2" s="43"/>
+      <c r="S2" s="43"/>
       <c r="T2" s="8" t="s">
         <v>30</v>
       </c>
@@ -1055,35 +1065,35 @@
       <c r="V2" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="X2" s="41" t="s">
+      <c r="AC2" s="42" t="s">
         <v>29</v>
       </c>
-      <c r="Y2" s="39"/>
-      <c r="Z2" s="39"/>
-      <c r="AA2" s="8" t="s">
+      <c r="AD2" s="43"/>
+      <c r="AE2" s="43"/>
+      <c r="AF2" s="8" t="s">
         <v>50</v>
       </c>
-      <c r="AB2" s="8"/>
-      <c r="AC2" s="8" t="s">
+      <c r="AG2" s="8"/>
+      <c r="AH2" s="8" t="s">
         <v>30</v>
       </c>
-      <c r="AD2" s="8" t="s">
+      <c r="AI2" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="AE2" s="8" t="s">
+      <c r="AJ2" s="8" t="s">
         <v>123</v>
       </c>
-      <c r="AF2" s="53" t="s">
+      <c r="AK2" s="34" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="3" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A3" s="35" t="s">
+    <row r="3" spans="1:37" x14ac:dyDescent="0.3">
+      <c r="A3" s="39" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="36"/>
-      <c r="C3" s="36"/>
-      <c r="D3" s="36"/>
+      <c r="B3" s="38"/>
+      <c r="C3" s="38"/>
+      <c r="D3" s="38"/>
       <c r="E3" s="21">
         <v>1.6</v>
       </c>
@@ -1091,19 +1101,19 @@
         <v>5</v>
       </c>
       <c r="G3" s="3"/>
-      <c r="I3" s="35" t="s">
+      <c r="I3" s="39" t="s">
         <v>23</v>
       </c>
-      <c r="J3" s="36"/>
-      <c r="K3" s="36"/>
-      <c r="L3" s="36"/>
-      <c r="M3" s="36"/>
-      <c r="N3" s="44"/>
-      <c r="Q3" s="35" t="s">
+      <c r="J3" s="38"/>
+      <c r="K3" s="38"/>
+      <c r="L3" s="38"/>
+      <c r="M3" s="38"/>
+      <c r="N3" s="45"/>
+      <c r="Q3" s="39" t="s">
         <v>32</v>
       </c>
-      <c r="R3" s="36"/>
-      <c r="S3" s="36"/>
+      <c r="R3" s="38"/>
+      <c r="S3" s="38"/>
       <c r="T3" s="1">
         <v>0.96</v>
       </c>
@@ -1114,59 +1124,59 @@
         <f>AVERAGE(T3:U3)</f>
         <v>0.97</v>
       </c>
-      <c r="X3" s="35" t="s">
+      <c r="AC3" s="39" t="s">
         <v>51</v>
       </c>
-      <c r="Y3" s="36"/>
-      <c r="Z3" s="36"/>
-      <c r="AA3" s="1">
+      <c r="AD3" s="38"/>
+      <c r="AE3" s="38"/>
+      <c r="AF3" s="1">
         <v>1.6</v>
       </c>
-      <c r="AB3" s="1">
+      <c r="AG3" s="1">
         <v>8</v>
       </c>
-      <c r="AC3" s="1">
-        <f>T3</f>
+      <c r="AH3" s="1">
+        <f t="shared" ref="AH3:AI5" si="0">T3</f>
         <v>0.96</v>
       </c>
-      <c r="AD3" s="1">
-        <f>U3</f>
+      <c r="AI3" s="1">
+        <f t="shared" si="0"/>
         <v>0.98</v>
       </c>
-      <c r="AE3" s="1">
-        <f>AD3+AF3*AA3</f>
+      <c r="AJ3" s="1">
+        <f>AI3+AK3*AF3</f>
         <v>0.98499999999999999</v>
       </c>
-      <c r="AF3" s="3">
-        <f>(AD3-AC3)/(AB3-AA3)</f>
+      <c r="AK3" s="3">
+        <f>(AI3-AH3)/(AG3-AF3)</f>
         <v>3.1250000000000028E-3</v>
       </c>
     </row>
-    <row r="4" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A4" s="35" t="s">
+    <row r="4" spans="1:37" x14ac:dyDescent="0.3">
+      <c r="A4" s="39" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="36"/>
-      <c r="C4" s="36"/>
-      <c r="D4" s="36"/>
-      <c r="E4" s="42" t="s">
+      <c r="B4" s="38"/>
+      <c r="C4" s="38"/>
+      <c r="D4" s="38"/>
+      <c r="E4" s="49" t="s">
         <v>2</v>
       </c>
-      <c r="F4" s="42"/>
-      <c r="G4" s="43"/>
-      <c r="I4" s="35" t="s">
+      <c r="F4" s="49"/>
+      <c r="G4" s="50"/>
+      <c r="I4" s="39" t="s">
         <v>24</v>
       </c>
-      <c r="J4" s="36"/>
-      <c r="K4" s="36"/>
-      <c r="L4" s="36"/>
-      <c r="M4" s="36"/>
-      <c r="N4" s="44"/>
-      <c r="Q4" s="35" t="s">
+      <c r="J4" s="38"/>
+      <c r="K4" s="38"/>
+      <c r="L4" s="38"/>
+      <c r="M4" s="38"/>
+      <c r="N4" s="45"/>
+      <c r="Q4" s="39" t="s">
         <v>56</v>
       </c>
-      <c r="R4" s="36"/>
-      <c r="S4" s="36"/>
+      <c r="R4" s="38"/>
+      <c r="S4" s="38"/>
       <c r="T4" s="1">
         <v>0.95</v>
       </c>
@@ -1174,44 +1184,44 @@
         <v>0.97</v>
       </c>
       <c r="V4" s="3">
-        <f t="shared" ref="V4:V12" si="0">AVERAGE(T4:U4)</f>
+        <f t="shared" ref="V4:V12" si="1">AVERAGE(T4:U4)</f>
         <v>0.96</v>
       </c>
-      <c r="X4" s="35" t="s">
+      <c r="AC4" s="39" t="s">
         <v>55</v>
       </c>
-      <c r="Y4" s="36"/>
-      <c r="Z4" s="36"/>
-      <c r="AA4" s="1">
+      <c r="AD4" s="38"/>
+      <c r="AE4" s="38"/>
+      <c r="AF4" s="1">
         <v>1</v>
       </c>
-      <c r="AB4" s="1">
+      <c r="AG4" s="1">
         <v>6.3</v>
       </c>
-      <c r="AC4" s="1">
-        <f>T4</f>
+      <c r="AH4" s="1">
+        <f t="shared" si="0"/>
         <v>0.95</v>
       </c>
-      <c r="AD4" s="1">
-        <f>U4</f>
+      <c r="AI4" s="1">
+        <f t="shared" si="0"/>
         <v>0.97</v>
       </c>
-      <c r="AE4" s="1">
-        <f t="shared" ref="AE4:AE10" si="1">AD4+AF4*AA4</f>
+      <c r="AJ4" s="1">
+        <f t="shared" ref="AJ4:AJ10" si="2">AI4+AK4*AF4</f>
         <v>0.97377358490566035</v>
       </c>
-      <c r="AF4" s="3">
-        <f t="shared" ref="AF4:AF10" si="2">(AD4-AC4)/(AB4-AA4)</f>
+      <c r="AK4" s="3">
+        <f t="shared" ref="AK4:AK10" si="3">(AI4-AH4)/(AG4-AF4)</f>
         <v>3.7735849056603809E-3</v>
       </c>
     </row>
-    <row r="5" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A5" s="35" t="s">
+    <row r="5" spans="1:37" x14ac:dyDescent="0.3">
+      <c r="A5" s="39" t="s">
         <v>6</v>
       </c>
-      <c r="B5" s="36"/>
-      <c r="C5" s="36"/>
-      <c r="D5" s="36"/>
+      <c r="B5" s="38"/>
+      <c r="C5" s="38"/>
+      <c r="D5" s="38"/>
       <c r="E5" s="22">
         <v>10000</v>
       </c>
@@ -1221,19 +1231,19 @@
       <c r="G5" s="3"/>
       <c r="I5" s="7"/>
       <c r="J5" s="1"/>
-      <c r="K5" s="36" t="s">
+      <c r="K5" s="38" t="s">
         <v>25</v>
       </c>
-      <c r="L5" s="36"/>
-      <c r="M5" s="36" t="s">
+      <c r="L5" s="38"/>
+      <c r="M5" s="38" t="s">
         <v>27</v>
       </c>
-      <c r="N5" s="44"/>
-      <c r="Q5" s="35" t="s">
+      <c r="N5" s="45"/>
+      <c r="Q5" s="39" t="s">
         <v>33</v>
       </c>
-      <c r="R5" s="36"/>
-      <c r="S5" s="36"/>
+      <c r="R5" s="38"/>
+      <c r="S5" s="38"/>
       <c r="T5" s="1">
         <v>0.95</v>
       </c>
@@ -1241,66 +1251,66 @@
         <v>0.97</v>
       </c>
       <c r="V5" s="3">
+        <f t="shared" si="1"/>
+        <v>0.96</v>
+      </c>
+      <c r="AC5" s="39" t="s">
+        <v>33</v>
+      </c>
+      <c r="AD5" s="38"/>
+      <c r="AE5" s="38"/>
+      <c r="AF5" s="1">
+        <v>3.15</v>
+      </c>
+      <c r="AG5" s="1">
+        <v>8</v>
+      </c>
+      <c r="AH5" s="1">
         <f t="shared" si="0"/>
-        <v>0.96</v>
-      </c>
-      <c r="X5" s="35" t="s">
-        <v>33</v>
-      </c>
-      <c r="Y5" s="36"/>
-      <c r="Z5" s="36"/>
-      <c r="AA5" s="1">
-        <v>3.15</v>
-      </c>
-      <c r="AB5" s="1">
-        <v>8</v>
-      </c>
-      <c r="AC5" s="1">
-        <f>T5</f>
         <v>0.95</v>
       </c>
-      <c r="AD5" s="1">
-        <f>U5</f>
+      <c r="AI5" s="1">
+        <f t="shared" si="0"/>
         <v>0.97</v>
       </c>
-      <c r="AE5" s="1">
-        <f t="shared" si="1"/>
+      <c r="AJ5" s="1">
+        <f t="shared" si="2"/>
         <v>0.98298969072164943</v>
       </c>
-      <c r="AF5" s="3">
-        <f t="shared" si="2"/>
+      <c r="AK5" s="3">
+        <f t="shared" si="3"/>
         <v>4.1237113402061891E-3</v>
       </c>
     </row>
-    <row r="6" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A6" s="35" t="s">
+    <row r="6" spans="1:37" x14ac:dyDescent="0.3">
+      <c r="A6" s="39" t="s">
         <v>7</v>
       </c>
-      <c r="B6" s="36"/>
-      <c r="C6" s="36"/>
-      <c r="D6" s="36"/>
+      <c r="B6" s="38"/>
+      <c r="C6" s="38"/>
+      <c r="D6" s="38"/>
       <c r="E6" s="22">
         <v>0.9</v>
       </c>
       <c r="F6" s="1"/>
       <c r="G6" s="3"/>
-      <c r="I6" s="35" t="s">
+      <c r="I6" s="39" t="s">
         <v>26</v>
       </c>
-      <c r="J6" s="36"/>
-      <c r="K6" s="42">
+      <c r="J6" s="38"/>
+      <c r="K6" s="49">
         <v>2</v>
       </c>
-      <c r="L6" s="42"/>
-      <c r="M6" s="36">
+      <c r="L6" s="49"/>
+      <c r="M6" s="38">
         <v>0.99</v>
       </c>
-      <c r="N6" s="44"/>
-      <c r="Q6" s="35" t="s">
+      <c r="N6" s="45"/>
+      <c r="Q6" s="39" t="s">
         <v>34</v>
       </c>
-      <c r="R6" s="36"/>
-      <c r="S6" s="36"/>
+      <c r="R6" s="38"/>
+      <c r="S6" s="38"/>
       <c r="T6" s="1">
         <v>0.92</v>
       </c>
@@ -1308,66 +1318,66 @@
         <v>0.96</v>
       </c>
       <c r="V6" s="3">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0.94</v>
       </c>
-      <c r="X6" s="35" t="s">
+      <c r="AC6" s="39" t="s">
         <v>52</v>
       </c>
-      <c r="Y6" s="36"/>
-      <c r="Z6" s="36"/>
-      <c r="AA6" s="1">
+      <c r="AD6" s="38"/>
+      <c r="AE6" s="38"/>
+      <c r="AF6" s="1">
         <v>12.5</v>
       </c>
-      <c r="AB6" s="1">
+      <c r="AG6" s="1">
         <v>31.5</v>
       </c>
-      <c r="AC6" s="1">
+      <c r="AH6" s="1">
         <f>T3*T3</f>
         <v>0.92159999999999997</v>
       </c>
-      <c r="AD6" s="1">
+      <c r="AI6" s="1">
         <f>U3*U3</f>
         <v>0.96039999999999992</v>
       </c>
-      <c r="AE6" s="1">
-        <f t="shared" si="1"/>
+      <c r="AJ6" s="1">
+        <f t="shared" si="2"/>
         <v>0.98592631578947354</v>
       </c>
-      <c r="AF6" s="3">
-        <f t="shared" si="2"/>
+      <c r="AK6" s="3">
+        <f t="shared" si="3"/>
         <v>2.042105263157892E-3</v>
       </c>
     </row>
-    <row r="7" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A7" s="35" t="s">
+    <row r="7" spans="1:37" x14ac:dyDescent="0.3">
+      <c r="A7" s="39" t="s">
         <v>8</v>
       </c>
-      <c r="B7" s="36"/>
-      <c r="C7" s="36"/>
-      <c r="D7" s="36"/>
+      <c r="B7" s="38"/>
+      <c r="C7" s="38"/>
+      <c r="D7" s="38"/>
       <c r="E7" s="22">
         <v>3</v>
       </c>
       <c r="F7" s="1"/>
       <c r="G7" s="3"/>
-      <c r="I7" s="35" t="s">
+      <c r="I7" s="39" t="s">
         <v>28</v>
       </c>
-      <c r="J7" s="36"/>
-      <c r="K7" s="42">
+      <c r="J7" s="38"/>
+      <c r="K7" s="49">
         <v>2</v>
       </c>
-      <c r="L7" s="42"/>
-      <c r="M7" s="36">
+      <c r="L7" s="49"/>
+      <c r="M7" s="38">
         <v>0.98</v>
       </c>
-      <c r="N7" s="44"/>
-      <c r="Q7" s="35" t="s">
+      <c r="N7" s="45"/>
+      <c r="Q7" s="39" t="s">
         <v>35</v>
       </c>
-      <c r="R7" s="36"/>
-      <c r="S7" s="36"/>
+      <c r="R7" s="38"/>
+      <c r="S7" s="38"/>
       <c r="T7" s="1">
         <v>0.72</v>
       </c>
@@ -1375,67 +1385,67 @@
         <v>0.82</v>
       </c>
       <c r="V7" s="3">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0.77</v>
       </c>
-      <c r="X7" s="35" t="s">
+      <c r="AC7" s="39" t="s">
         <v>34</v>
       </c>
-      <c r="Y7" s="36"/>
-      <c r="Z7" s="36"/>
-      <c r="AA7" s="1">
+      <c r="AD7" s="38"/>
+      <c r="AE7" s="38"/>
+      <c r="AF7" s="1">
         <v>16</v>
       </c>
-      <c r="AB7" s="1">
+      <c r="AG7" s="1">
         <v>63</v>
       </c>
-      <c r="AC7" s="1">
+      <c r="AH7" s="1">
         <f>T6</f>
         <v>0.92</v>
       </c>
-      <c r="AD7" s="1">
+      <c r="AI7" s="1">
         <f>U6</f>
         <v>0.96</v>
       </c>
-      <c r="AE7" s="1">
-        <f t="shared" si="1"/>
+      <c r="AJ7" s="1">
+        <f t="shared" si="2"/>
         <v>0.97361702127659566</v>
       </c>
-      <c r="AF7" s="3">
-        <f t="shared" si="2"/>
+      <c r="AK7" s="3">
+        <f t="shared" si="3"/>
         <v>8.5106382978723241E-4</v>
       </c>
     </row>
-    <row r="8" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A8" s="37" t="s">
+    <row r="8" spans="1:37" x14ac:dyDescent="0.3">
+      <c r="A8" s="40" t="s">
         <v>9</v>
       </c>
-      <c r="B8" s="38"/>
-      <c r="C8" s="38"/>
-      <c r="D8" s="38"/>
+      <c r="B8" s="41"/>
+      <c r="C8" s="41"/>
+      <c r="D8" s="41"/>
       <c r="E8" s="23">
         <v>2.2000000000000002</v>
       </c>
       <c r="F8" s="4"/>
       <c r="G8" s="5"/>
-      <c r="I8" s="35" t="s">
+      <c r="I8" s="39" t="s">
         <v>29</v>
       </c>
-      <c r="J8" s="36"/>
-      <c r="K8" s="42">
-        <v>0</v>
-      </c>
-      <c r="L8" s="42"/>
-      <c r="M8" s="42">
+      <c r="J8" s="38"/>
+      <c r="K8" s="49">
+        <v>0</v>
+      </c>
+      <c r="L8" s="49"/>
+      <c r="M8" s="49">
         <f>V11</f>
         <v>0.95</v>
       </c>
-      <c r="N8" s="43"/>
-      <c r="Q8" s="35" t="s">
+      <c r="N8" s="50"/>
+      <c r="Q8" s="39" t="s">
         <v>36</v>
       </c>
-      <c r="R8" s="36"/>
-      <c r="S8" s="36"/>
+      <c r="R8" s="38"/>
+      <c r="S8" s="38"/>
       <c r="T8" s="1">
         <v>0.7</v>
       </c>
@@ -1443,63 +1453,63 @@
         <v>0.8</v>
       </c>
       <c r="V8" s="3">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0.75</v>
       </c>
-      <c r="X8" s="35" t="s">
+      <c r="AC8" s="39" t="s">
         <v>53</v>
       </c>
-      <c r="Y8" s="36"/>
-      <c r="Z8" s="36"/>
-      <c r="AA8" s="1">
+      <c r="AD8" s="38"/>
+      <c r="AE8" s="38"/>
+      <c r="AF8" s="1">
         <v>10</v>
       </c>
-      <c r="AB8" s="1">
+      <c r="AG8" s="1">
         <v>30</v>
       </c>
-      <c r="AC8" s="1">
+      <c r="AH8" s="1">
         <f>T4*T3</f>
         <v>0.91199999999999992</v>
       </c>
-      <c r="AD8" s="1">
+      <c r="AI8" s="1">
         <f>U4*U3</f>
         <v>0.9506</v>
       </c>
-      <c r="AE8" s="1">
-        <f t="shared" si="1"/>
+      <c r="AJ8" s="1">
+        <f t="shared" si="2"/>
         <v>0.96989999999999998</v>
       </c>
-      <c r="AF8" s="3">
-        <f t="shared" si="2"/>
+      <c r="AK8" s="3">
+        <f t="shared" si="3"/>
         <v>1.930000000000004E-3</v>
       </c>
     </row>
-    <row r="9" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A9" s="35" t="s">
+    <row r="9" spans="1:37" x14ac:dyDescent="0.3">
+      <c r="A9" s="39" t="s">
         <v>14</v>
       </c>
-      <c r="B9" s="36"/>
-      <c r="C9" s="36"/>
-      <c r="D9" s="36"/>
-      <c r="E9" s="36"/>
-      <c r="F9" s="36"/>
+      <c r="B9" s="38"/>
+      <c r="C9" s="38"/>
+      <c r="D9" s="38"/>
+      <c r="E9" s="38"/>
+      <c r="F9" s="38"/>
       <c r="G9" s="3"/>
-      <c r="I9" s="35" t="s">
+      <c r="I9" s="39" t="s">
         <v>57</v>
       </c>
-      <c r="J9" s="36"/>
-      <c r="K9" s="36"/>
-      <c r="L9" s="36"/>
-      <c r="M9" s="45">
+      <c r="J9" s="38"/>
+      <c r="K9" s="38"/>
+      <c r="L9" s="38"/>
+      <c r="M9" s="55">
         <f>M7^K7*M6^K6*M8^K8</f>
         <v>0.94128803999999988</v>
       </c>
-      <c r="N9" s="46"/>
-      <c r="Q9" s="35" t="s">
+      <c r="N9" s="56"/>
+      <c r="Q9" s="39" t="s">
         <v>37</v>
       </c>
-      <c r="R9" s="36"/>
-      <c r="S9" s="36"/>
+      <c r="R9" s="38"/>
+      <c r="S9" s="38"/>
       <c r="T9" s="1">
         <v>0.75</v>
       </c>
@@ -1507,38 +1517,38 @@
         <v>0.85</v>
       </c>
       <c r="V9" s="3">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0.8</v>
       </c>
-      <c r="X9" s="35" t="s">
+      <c r="AC9" s="39" t="s">
         <v>54</v>
       </c>
-      <c r="Y9" s="36"/>
-      <c r="Z9" s="36"/>
-      <c r="AA9" s="1">
+      <c r="AD9" s="38"/>
+      <c r="AE9" s="38"/>
+      <c r="AF9" s="1">
         <v>8</v>
       </c>
-      <c r="AB9" s="1">
+      <c r="AG9" s="1">
         <v>63</v>
       </c>
-      <c r="AC9" s="1">
+      <c r="AH9" s="1">
         <f>T8</f>
         <v>0.7</v>
       </c>
-      <c r="AD9" s="1">
+      <c r="AI9" s="1">
         <f>U10</f>
         <v>0.9</v>
       </c>
-      <c r="AE9" s="1">
-        <f t="shared" si="1"/>
+      <c r="AJ9" s="1">
+        <f t="shared" si="2"/>
         <v>0.92909090909090908</v>
       </c>
-      <c r="AF9" s="3">
-        <f t="shared" si="2"/>
+      <c r="AK9" s="3">
+        <f t="shared" si="3"/>
         <v>3.6363636363636377E-3</v>
       </c>
     </row>
-    <row r="10" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A10" s="9" t="s">
         <v>12</v>
       </c>
@@ -1548,21 +1558,21 @@
       <c r="E10" s="10"/>
       <c r="F10" s="10"/>
       <c r="G10" s="11"/>
-      <c r="I10" s="35" t="s">
+      <c r="I10" s="39" t="s">
         <v>58</v>
       </c>
-      <c r="J10" s="36"/>
-      <c r="K10" s="36"/>
-      <c r="L10" s="36"/>
-      <c r="M10" s="42">
+      <c r="J10" s="38"/>
+      <c r="K10" s="38"/>
+      <c r="L10" s="38"/>
+      <c r="M10" s="49">
         <v>0.97</v>
       </c>
-      <c r="N10" s="43"/>
-      <c r="Q10" s="35" t="s">
+      <c r="N10" s="50"/>
+      <c r="Q10" s="39" t="s">
         <v>38</v>
       </c>
-      <c r="R10" s="36"/>
-      <c r="S10" s="36"/>
+      <c r="R10" s="38"/>
+      <c r="S10" s="38"/>
       <c r="T10" s="1">
         <v>0.8</v>
       </c>
@@ -1570,63 +1580,63 @@
         <v>0.9</v>
       </c>
       <c r="V10" s="3">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0.85000000000000009</v>
       </c>
-      <c r="X10" s="37" t="s">
+      <c r="AC10" s="40" t="s">
         <v>35</v>
       </c>
-      <c r="Y10" s="38"/>
-      <c r="Z10" s="38"/>
-      <c r="AA10" s="4">
+      <c r="AD10" s="41"/>
+      <c r="AE10" s="41"/>
+      <c r="AF10" s="4">
         <v>70</v>
       </c>
-      <c r="AB10" s="4">
+      <c r="AG10" s="4">
         <v>320</v>
       </c>
-      <c r="AC10" s="4">
+      <c r="AH10" s="4">
         <f>T7</f>
         <v>0.72</v>
       </c>
-      <c r="AD10" s="4">
+      <c r="AI10" s="4">
         <f>U7</f>
         <v>0.82</v>
       </c>
-      <c r="AE10" s="4">
-        <f t="shared" si="1"/>
+      <c r="AJ10" s="4">
+        <f t="shared" si="2"/>
         <v>0.84799999999999998</v>
       </c>
-      <c r="AF10" s="5">
-        <f t="shared" si="2"/>
+      <c r="AK10" s="5">
+        <f t="shared" si="3"/>
         <v>3.9999999999999991E-4</v>
       </c>
     </row>
-    <row r="11" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A11" s="37" t="s">
+    <row r="11" spans="1:37" x14ac:dyDescent="0.3">
+      <c r="A11" s="40" t="s">
         <v>13</v>
       </c>
-      <c r="B11" s="38"/>
-      <c r="C11" s="38"/>
-      <c r="D11" s="38"/>
-      <c r="E11" s="38"/>
-      <c r="F11" s="38"/>
+      <c r="B11" s="41"/>
+      <c r="C11" s="41"/>
+      <c r="D11" s="41"/>
+      <c r="E11" s="41"/>
+      <c r="F11" s="41"/>
       <c r="G11" s="5"/>
-      <c r="I11" s="37" t="s">
+      <c r="I11" s="40" t="s">
         <v>62</v>
       </c>
-      <c r="J11" s="38"/>
-      <c r="K11" s="38"/>
-      <c r="L11" s="38"/>
-      <c r="M11" s="50">
+      <c r="J11" s="41"/>
+      <c r="K11" s="41"/>
+      <c r="L11" s="41"/>
+      <c r="M11" s="51">
         <f>M2/M10/M9</f>
         <v>7.0094783572623509</v>
       </c>
-      <c r="N11" s="51"/>
-      <c r="Q11" s="35" t="s">
+      <c r="N11" s="52"/>
+      <c r="Q11" s="39" t="s">
         <v>39</v>
       </c>
-      <c r="R11" s="36"/>
-      <c r="S11" s="36"/>
+      <c r="R11" s="38"/>
+      <c r="S11" s="38"/>
       <c r="T11" s="1">
         <v>0.94</v>
       </c>
@@ -1634,33 +1644,33 @@
         <v>0.96</v>
       </c>
       <c r="V11" s="3">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0.95</v>
       </c>
-      <c r="X11" s="17"/>
-      <c r="Y11" s="17"/>
-      <c r="Z11" s="17"/>
-      <c r="AA11" s="1"/>
-      <c r="AB11" s="1"/>
-      <c r="AC11" s="1"/>
-    </row>
-    <row r="12" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A12" s="41" t="s">
+      <c r="AC11" s="17"/>
+      <c r="AD11" s="17"/>
+      <c r="AE11" s="17"/>
+      <c r="AF11" s="1"/>
+      <c r="AG11" s="1"/>
+      <c r="AH11" s="1"/>
+    </row>
+    <row r="12" spans="1:37" x14ac:dyDescent="0.3">
+      <c r="A12" s="42" t="s">
         <v>17</v>
       </c>
-      <c r="B12" s="39"/>
-      <c r="C12" s="39"/>
-      <c r="D12" s="39"/>
-      <c r="E12" s="39" t="s">
+      <c r="B12" s="43"/>
+      <c r="C12" s="43"/>
+      <c r="D12" s="43"/>
+      <c r="E12" s="43" t="s">
         <v>18</v>
       </c>
-      <c r="F12" s="39"/>
-      <c r="G12" s="40"/>
-      <c r="Q12" s="37" t="s">
+      <c r="F12" s="43"/>
+      <c r="G12" s="44"/>
+      <c r="Q12" s="40" t="s">
         <v>40</v>
       </c>
-      <c r="R12" s="38"/>
-      <c r="S12" s="38"/>
+      <c r="R12" s="41"/>
+      <c r="S12" s="41"/>
       <c r="T12" s="4">
         <v>0.92</v>
       </c>
@@ -1668,20 +1678,20 @@
         <v>0.95</v>
       </c>
       <c r="V12" s="5">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0.93500000000000005</v>
       </c>
-      <c r="X12" t="s">
+      <c r="AC12" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="13" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A13" s="35" t="s">
+    <row r="13" spans="1:37" x14ac:dyDescent="0.3">
+      <c r="A13" s="39" t="s">
         <v>19</v>
       </c>
-      <c r="B13" s="36"/>
-      <c r="C13" s="36"/>
-      <c r="D13" s="36"/>
+      <c r="B13" s="38"/>
+      <c r="C13" s="38"/>
+      <c r="D13" s="38"/>
       <c r="E13" s="22">
         <v>400</v>
       </c>
@@ -1691,17 +1701,17 @@
       <c r="G13" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="X13" t="s">
+      <c r="AC13" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="14" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A14" s="35" t="s">
+    <row r="14" spans="1:37" x14ac:dyDescent="0.3">
+      <c r="A14" s="39" t="s">
         <v>15</v>
       </c>
-      <c r="B14" s="36"/>
-      <c r="C14" s="36"/>
-      <c r="D14" s="36"/>
+      <c r="B14" s="38"/>
+      <c r="C14" s="38"/>
+      <c r="D14" s="38"/>
       <c r="E14" s="22">
         <v>400</v>
       </c>
@@ -1710,13 +1720,13 @@
       </c>
       <c r="G14" s="3"/>
     </row>
-    <row r="15" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A15" s="37" t="s">
+    <row r="15" spans="1:37" x14ac:dyDescent="0.3">
+      <c r="A15" s="40" t="s">
         <v>21</v>
       </c>
-      <c r="B15" s="38"/>
-      <c r="C15" s="38"/>
-      <c r="D15" s="38"/>
+      <c r="B15" s="41"/>
+      <c r="C15" s="41"/>
+      <c r="D15" s="41"/>
       <c r="E15" s="23">
         <v>300</v>
       </c>
@@ -1728,90 +1738,90 @@
     <row r="19" spans="9:26" x14ac:dyDescent="0.3">
       <c r="I19" s="12"/>
       <c r="J19" s="8"/>
-      <c r="K19" s="41">
+      <c r="K19" s="42">
         <v>3000</v>
       </c>
-      <c r="L19" s="39"/>
-      <c r="M19" s="39"/>
-      <c r="N19" s="40"/>
-      <c r="O19" s="39">
+      <c r="L19" s="43"/>
+      <c r="M19" s="43"/>
+      <c r="N19" s="44"/>
+      <c r="O19" s="43">
         <v>1500</v>
       </c>
-      <c r="P19" s="39"/>
-      <c r="Q19" s="39"/>
-      <c r="R19" s="39"/>
-      <c r="S19" s="41">
+      <c r="P19" s="43"/>
+      <c r="Q19" s="43"/>
+      <c r="R19" s="43"/>
+      <c r="S19" s="42">
         <v>1000</v>
       </c>
-      <c r="T19" s="39"/>
-      <c r="U19" s="39"/>
-      <c r="V19" s="39"/>
-      <c r="W19" s="41">
+      <c r="T19" s="43"/>
+      <c r="U19" s="43"/>
+      <c r="V19" s="44"/>
+      <c r="W19" s="43">
         <v>750</v>
       </c>
-      <c r="X19" s="39"/>
-      <c r="Y19" s="39"/>
-      <c r="Z19" s="40"/>
+      <c r="X19" s="43"/>
+      <c r="Y19" s="43"/>
+      <c r="Z19" s="44"/>
     </row>
     <row r="20" spans="9:26" x14ac:dyDescent="0.3">
-      <c r="I20" s="35" t="s">
+      <c r="I20" s="39" t="s">
         <v>64</v>
       </c>
-      <c r="J20" s="36"/>
-      <c r="K20" s="7" t="s">
+      <c r="J20" s="38"/>
+      <c r="K20" s="13" t="s">
         <v>80</v>
       </c>
-      <c r="L20" s="1" t="s">
+      <c r="L20" s="4" t="s">
         <v>78</v>
       </c>
-      <c r="M20" s="1" t="s">
+      <c r="M20" s="4" t="s">
         <v>79</v>
       </c>
-      <c r="N20" s="3" t="s">
+      <c r="N20" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="O20" s="1" t="s">
+      <c r="O20" s="4" t="s">
         <v>80</v>
       </c>
-      <c r="P20" s="1" t="s">
+      <c r="P20" s="4" t="s">
         <v>78</v>
       </c>
-      <c r="Q20" s="1" t="s">
+      <c r="Q20" s="4" t="s">
         <v>79</v>
       </c>
-      <c r="R20" s="1" t="s">
+      <c r="R20" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="S20" s="1" t="s">
+      <c r="S20" s="13" t="s">
         <v>80</v>
       </c>
-      <c r="T20" s="1" t="s">
+      <c r="T20" s="4" t="s">
         <v>78</v>
       </c>
-      <c r="U20" s="1" t="s">
+      <c r="U20" s="4" t="s">
         <v>79</v>
       </c>
-      <c r="V20" s="1" t="s">
+      <c r="V20" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="W20" s="1" t="s">
+      <c r="W20" s="4" t="s">
         <v>80</v>
       </c>
-      <c r="X20" s="1" t="s">
+      <c r="X20" s="4" t="s">
         <v>78</v>
       </c>
-      <c r="Y20" s="1" t="s">
+      <c r="Y20" s="4" t="s">
         <v>79</v>
       </c>
-      <c r="Z20" s="1" t="s">
+      <c r="Z20" s="5" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="21" spans="9:26" x14ac:dyDescent="0.3">
-      <c r="I21" s="35">
+      <c r="I21" s="39">
         <v>0.37</v>
       </c>
-      <c r="J21" s="36"/>
+      <c r="J21" s="38"/>
       <c r="K21" s="27" t="s">
         <v>65</v>
       </c>
@@ -1839,17 +1849,17 @@
       <c r="S21" s="7"/>
       <c r="T21" s="1"/>
       <c r="U21" s="1"/>
-      <c r="V21" s="1"/>
-      <c r="W21" s="7"/>
+      <c r="V21" s="3"/>
+      <c r="W21" s="1"/>
       <c r="X21" s="1"/>
       <c r="Y21" s="1"/>
       <c r="Z21" s="3"/>
     </row>
     <row r="22" spans="9:26" x14ac:dyDescent="0.3">
-      <c r="I22" s="35">
+      <c r="I22" s="39">
         <v>0.55000000000000004</v>
       </c>
-      <c r="J22" s="36"/>
+      <c r="J22" s="38"/>
       <c r="K22" s="27" t="s">
         <v>65</v>
       </c>
@@ -1875,17 +1885,17 @@
       <c r="S22" s="7"/>
       <c r="T22" s="1"/>
       <c r="U22" s="1"/>
-      <c r="V22" s="1"/>
-      <c r="W22" s="7"/>
+      <c r="V22" s="3"/>
+      <c r="W22" s="1"/>
       <c r="X22" s="1"/>
       <c r="Y22" s="1"/>
       <c r="Z22" s="3"/>
     </row>
     <row r="23" spans="9:26" x14ac:dyDescent="0.3">
-      <c r="I23" s="35">
+      <c r="I23" s="39">
         <v>0.75</v>
       </c>
-      <c r="J23" s="36"/>
+      <c r="J23" s="38"/>
       <c r="K23" s="7" t="s">
         <v>66</v>
       </c>
@@ -1911,17 +1921,17 @@
       <c r="S23" s="7"/>
       <c r="T23" s="1"/>
       <c r="U23" s="1"/>
-      <c r="V23" s="1"/>
-      <c r="W23" s="7"/>
+      <c r="V23" s="3"/>
+      <c r="W23" s="1"/>
       <c r="X23" s="1"/>
       <c r="Y23" s="1"/>
       <c r="Z23" s="3"/>
     </row>
     <row r="24" spans="9:26" x14ac:dyDescent="0.3">
-      <c r="I24" s="35">
+      <c r="I24" s="39">
         <v>1.1000000000000001</v>
       </c>
-      <c r="J24" s="36"/>
+      <c r="J24" s="38"/>
       <c r="K24" s="7" t="s">
         <v>67</v>
       </c>
@@ -1947,17 +1957,17 @@
       <c r="S24" s="7"/>
       <c r="T24" s="1"/>
       <c r="U24" s="1"/>
-      <c r="V24" s="1"/>
-      <c r="W24" s="7"/>
+      <c r="V24" s="3"/>
+      <c r="W24" s="1"/>
       <c r="X24" s="1"/>
       <c r="Y24" s="1"/>
       <c r="Z24" s="3"/>
     </row>
     <row r="25" spans="9:26" x14ac:dyDescent="0.3">
-      <c r="I25" s="35">
+      <c r="I25" s="39">
         <v>1.5</v>
       </c>
-      <c r="J25" s="36"/>
+      <c r="J25" s="38"/>
       <c r="K25" s="7" t="s">
         <v>68</v>
       </c>
@@ -1983,17 +1993,17 @@
       <c r="S25" s="7"/>
       <c r="T25" s="1"/>
       <c r="U25" s="1"/>
-      <c r="V25" s="1"/>
-      <c r="W25" s="7"/>
+      <c r="V25" s="3"/>
+      <c r="W25" s="1"/>
       <c r="X25" s="1"/>
       <c r="Y25" s="1"/>
       <c r="Z25" s="3"/>
     </row>
     <row r="26" spans="9:26" x14ac:dyDescent="0.3">
-      <c r="I26" s="35">
+      <c r="I26" s="39">
         <v>2.2000000000000002</v>
       </c>
-      <c r="J26" s="36"/>
+      <c r="J26" s="38"/>
       <c r="K26" s="7" t="s">
         <v>95</v>
       </c>
@@ -2019,17 +2029,17 @@
       <c r="S26" s="7"/>
       <c r="T26" s="1"/>
       <c r="U26" s="1"/>
-      <c r="V26" s="1"/>
-      <c r="W26" s="7"/>
+      <c r="V26" s="3"/>
+      <c r="W26" s="1"/>
       <c r="X26" s="1"/>
       <c r="Y26" s="1"/>
       <c r="Z26" s="3"/>
     </row>
     <row r="27" spans="9:26" x14ac:dyDescent="0.3">
-      <c r="I27" s="35">
+      <c r="I27" s="39">
         <v>3</v>
       </c>
-      <c r="J27" s="36"/>
+      <c r="J27" s="38"/>
       <c r="K27" s="7" t="s">
         <v>69</v>
       </c>
@@ -2053,17 +2063,17 @@
       <c r="S27" s="7"/>
       <c r="T27" s="1"/>
       <c r="U27" s="1"/>
-      <c r="V27" s="1"/>
-      <c r="W27" s="7"/>
+      <c r="V27" s="3"/>
+      <c r="W27" s="1"/>
       <c r="X27" s="1"/>
       <c r="Y27" s="1"/>
       <c r="Z27" s="3"/>
     </row>
     <row r="28" spans="9:26" x14ac:dyDescent="0.3">
-      <c r="I28" s="35">
+      <c r="I28" s="39">
         <v>4</v>
       </c>
-      <c r="J28" s="36"/>
+      <c r="J28" s="38"/>
       <c r="K28" s="7" t="s">
         <v>70</v>
       </c>
@@ -2087,17 +2097,17 @@
       <c r="S28" s="7"/>
       <c r="T28" s="1"/>
       <c r="U28" s="1"/>
-      <c r="V28" s="1"/>
-      <c r="W28" s="7"/>
+      <c r="V28" s="3"/>
+      <c r="W28" s="1"/>
       <c r="X28" s="1"/>
       <c r="Y28" s="1"/>
       <c r="Z28" s="3"/>
     </row>
     <row r="29" spans="9:26" x14ac:dyDescent="0.3">
-      <c r="I29" s="35">
+      <c r="I29" s="39">
         <v>5.5</v>
       </c>
-      <c r="J29" s="36"/>
+      <c r="J29" s="38"/>
       <c r="K29" s="7" t="s">
         <v>71</v>
       </c>
@@ -2131,10 +2141,10 @@
       <c r="U29" s="26">
         <v>2.2000000000000002</v>
       </c>
-      <c r="V29" s="26">
+      <c r="V29" s="24">
         <v>0.85</v>
       </c>
-      <c r="W29" s="7" t="s">
+      <c r="W29" s="1" t="s">
         <v>99</v>
       </c>
       <c r="X29" s="26">
@@ -2148,10 +2158,10 @@
       </c>
     </row>
     <row r="30" spans="9:26" x14ac:dyDescent="0.3">
-      <c r="I30" s="35">
+      <c r="I30" s="39">
         <v>7.5</v>
       </c>
-      <c r="J30" s="36"/>
+      <c r="J30" s="38"/>
       <c r="K30" s="7" t="s">
         <v>72</v>
       </c>
@@ -2185,10 +2195,10 @@
       <c r="U30" s="26">
         <v>2.2000000000000002</v>
       </c>
-      <c r="V30" s="26">
+      <c r="V30" s="24">
         <v>0.86</v>
       </c>
-      <c r="W30" s="7" t="s">
+      <c r="W30" s="1" t="s">
         <v>100</v>
       </c>
       <c r="X30" s="26">
@@ -2202,10 +2212,10 @@
       </c>
     </row>
     <row r="31" spans="9:26" x14ac:dyDescent="0.3">
-      <c r="I31" s="35">
+      <c r="I31" s="39">
         <v>11</v>
       </c>
-      <c r="J31" s="36"/>
+      <c r="J31" s="38"/>
       <c r="K31" s="7" t="s">
         <v>73</v>
       </c>
@@ -2239,10 +2249,10 @@
       <c r="U31" s="26">
         <v>2.5</v>
       </c>
-      <c r="V31" s="1">
+      <c r="V31" s="3">
         <v>0.86799999999999999</v>
       </c>
-      <c r="W31" s="7" t="s">
+      <c r="W31" s="1" t="s">
         <v>101</v>
       </c>
       <c r="X31" s="26">
@@ -2256,10 +2266,10 @@
       </c>
     </row>
     <row r="32" spans="9:26" x14ac:dyDescent="0.3">
-      <c r="I32" s="35">
+      <c r="I32" s="39">
         <v>15</v>
       </c>
-      <c r="J32" s="36"/>
+      <c r="J32" s="38"/>
       <c r="K32" s="7" t="s">
         <v>74</v>
       </c>
@@ -2283,17 +2293,17 @@
       <c r="S32" s="7"/>
       <c r="T32" s="1"/>
       <c r="U32" s="1"/>
-      <c r="V32" s="1"/>
-      <c r="W32" s="7"/>
+      <c r="V32" s="3"/>
+      <c r="W32" s="1"/>
       <c r="X32" s="1"/>
       <c r="Y32" s="1"/>
       <c r="Z32" s="3"/>
     </row>
     <row r="33" spans="2:26" x14ac:dyDescent="0.3">
-      <c r="I33" s="35">
+      <c r="I33" s="39">
         <v>18.5</v>
       </c>
-      <c r="J33" s="36"/>
+      <c r="J33" s="38"/>
       <c r="K33" s="7" t="s">
         <v>75</v>
       </c>
@@ -2317,17 +2327,17 @@
       <c r="S33" s="7"/>
       <c r="T33" s="1"/>
       <c r="U33" s="1"/>
-      <c r="V33" s="1"/>
-      <c r="W33" s="7"/>
+      <c r="V33" s="3"/>
+      <c r="W33" s="1"/>
       <c r="X33" s="1"/>
       <c r="Y33" s="1"/>
       <c r="Z33" s="3"/>
     </row>
     <row r="34" spans="2:26" x14ac:dyDescent="0.3">
-      <c r="I34" s="35">
+      <c r="I34" s="39">
         <v>22</v>
       </c>
-      <c r="J34" s="36"/>
+      <c r="J34" s="38"/>
       <c r="K34" s="7" t="s">
         <v>76</v>
       </c>
@@ -2351,17 +2361,17 @@
       <c r="S34" s="7"/>
       <c r="T34" s="1"/>
       <c r="U34" s="1"/>
-      <c r="V34" s="1"/>
-      <c r="W34" s="7"/>
+      <c r="V34" s="3"/>
+      <c r="W34" s="1"/>
       <c r="X34" s="1"/>
       <c r="Y34" s="1"/>
       <c r="Z34" s="3"/>
     </row>
     <row r="35" spans="2:26" x14ac:dyDescent="0.3">
-      <c r="I35" s="37">
+      <c r="I35" s="40">
         <v>30</v>
       </c>
-      <c r="J35" s="38"/>
+      <c r="J35" s="41"/>
       <c r="K35" s="13" t="s">
         <v>77</v>
       </c>
@@ -2385,96 +2395,96 @@
       <c r="S35" s="13"/>
       <c r="T35" s="4"/>
       <c r="U35" s="4"/>
-      <c r="V35" s="4"/>
-      <c r="W35" s="13"/>
+      <c r="V35" s="5"/>
+      <c r="W35" s="4"/>
       <c r="X35" s="4"/>
       <c r="Y35" s="4"/>
       <c r="Z35" s="5"/>
     </row>
     <row r="36" spans="2:26" x14ac:dyDescent="0.3">
-      <c r="G36" s="47" t="s">
+      <c r="G36" s="57" t="s">
         <v>111</v>
       </c>
-      <c r="H36" s="47"/>
-      <c r="I36" s="39">
+      <c r="H36" s="57"/>
+      <c r="I36" s="47">
         <f>_xlfn.MINIFS(I21:J35,I21:J35,"&gt;="&amp;M11)</f>
         <v>7.5</v>
       </c>
-      <c r="J36" s="39"/>
-      <c r="K36" t="str">
+      <c r="J36" s="48"/>
+      <c r="K36" s="10" t="str">
         <f>VLOOKUP($I$36,$I$21:$R$35,3)</f>
         <v>112M2</v>
       </c>
-      <c r="L36">
+      <c r="L36" s="10">
         <f>VLOOKUP($I$36,$I$21:$R$35,4)</f>
         <v>2895</v>
       </c>
-      <c r="M36">
+      <c r="M36" s="10">
         <f>VLOOKUP($I$36,$I$21:$R$35,5)</f>
         <v>2.2000000000000002</v>
       </c>
-      <c r="N36">
+      <c r="N36" s="10">
         <f>VLOOKUP($I$36,$I$21:$R$35,6)</f>
         <v>0.87</v>
       </c>
-      <c r="O36" s="33" t="str">
+      <c r="O36" s="37" t="str">
         <f>VLOOKUP($I$36,$I$21:$R$35,7)</f>
         <v>132S4</v>
       </c>
-      <c r="P36" s="33">
+      <c r="P36" s="37">
         <f>VLOOKUP($I$36,$I$21:$R$35,8)</f>
         <v>1440</v>
       </c>
-      <c r="Q36" s="33">
+      <c r="Q36" s="37">
         <f>VLOOKUP($I$36,$I$21:$R$35,9)</f>
         <v>2.2000000000000002</v>
       </c>
-      <c r="R36" s="33">
+      <c r="R36" s="37">
         <f>VLOOKUP($I$36,$I$21:$R$35,10)</f>
         <v>0.872</v>
       </c>
-      <c r="S36" t="str">
+      <c r="S36" s="10" t="str">
         <f>VLOOKUP($I$36,$I$21:$Z$35,11)</f>
         <v>132M6</v>
       </c>
-      <c r="T36">
+      <c r="T36" s="10">
         <f>VLOOKUP($I$36,$I$21:$Z$35,12)</f>
         <v>960</v>
       </c>
-      <c r="U36">
+      <c r="U36" s="10">
         <f>VLOOKUP($I$36,$I$21:$Z$35,13)</f>
         <v>2.2000000000000002</v>
       </c>
-      <c r="V36">
+      <c r="V36" s="10">
         <f>VLOOKUP($I$36,$I$21:$Z$35,14)</f>
         <v>0.86</v>
       </c>
-      <c r="W36" t="str">
+      <c r="W36" s="10" t="str">
         <f>VLOOKUP($I$36,$I$21:$Z$35,15)</f>
         <v>160S8</v>
       </c>
-      <c r="X36">
+      <c r="X36" s="10">
         <f>VLOOKUP($I$36,$I$21:$Z$35,16)</f>
         <v>727</v>
       </c>
-      <c r="Y36">
+      <c r="Y36" s="10">
         <f>VLOOKUP($I$36,$I$21:$Z$35,17)</f>
         <v>2.4</v>
       </c>
-      <c r="Z36">
+      <c r="Z36" s="11">
         <f>VLOOKUP($I$36,$I$21:$Z$35,18)</f>
         <v>0.85</v>
       </c>
     </row>
     <row r="38" spans="2:26" x14ac:dyDescent="0.3">
-      <c r="B38" s="41" t="s">
+      <c r="B38" s="42" t="s">
         <v>45</v>
       </c>
-      <c r="C38" s="39"/>
-      <c r="D38" s="39"/>
-      <c r="E38" s="39"/>
-      <c r="F38" s="39"/>
-      <c r="G38" s="39"/>
+      <c r="C38" s="43"/>
+      <c r="D38" s="43"/>
+      <c r="E38" s="43"/>
+      <c r="F38" s="43"/>
+      <c r="G38" s="43"/>
       <c r="H38" s="8"/>
       <c r="I38" s="8"/>
       <c r="J38" s="8"/>
@@ -2496,19 +2506,19 @@
       <c r="Z38" s="6"/>
     </row>
     <row r="39" spans="2:26" x14ac:dyDescent="0.3">
-      <c r="B39" s="35" t="s">
+      <c r="B39" s="39" t="s">
         <v>48</v>
       </c>
-      <c r="C39" s="36"/>
-      <c r="D39" s="36"/>
-      <c r="E39" s="36"/>
-      <c r="F39" s="36"/>
-      <c r="G39" s="36"/>
-      <c r="H39" s="36" t="s">
+      <c r="C39" s="38"/>
+      <c r="D39" s="38"/>
+      <c r="E39" s="38"/>
+      <c r="F39" s="38"/>
+      <c r="G39" s="38"/>
+      <c r="H39" s="38" t="s">
         <v>49</v>
       </c>
-      <c r="I39" s="36"/>
-      <c r="J39" s="36"/>
+      <c r="I39" s="38"/>
+      <c r="J39" s="38"/>
       <c r="K39" s="7"/>
       <c r="L39" s="1"/>
       <c r="M39" s="1"/>
@@ -2539,25 +2549,25 @@
       </c>
     </row>
     <row r="40" spans="2:26" x14ac:dyDescent="0.3">
-      <c r="B40" s="35" t="s">
+      <c r="B40" s="39" t="s">
         <v>41</v>
       </c>
-      <c r="C40" s="36"/>
+      <c r="C40" s="38"/>
       <c r="D40" s="1" t="s">
         <v>44</v>
       </c>
       <c r="E40" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="F40" s="36" t="s">
+      <c r="F40" s="38" t="s">
         <v>43</v>
       </c>
-      <c r="G40" s="36"/>
-      <c r="H40" s="36" t="s">
+      <c r="G40" s="38"/>
+      <c r="H40" s="38" t="s">
         <v>47</v>
       </c>
-      <c r="I40" s="36"/>
-      <c r="J40" s="36"/>
+      <c r="I40" s="38"/>
+      <c r="J40" s="38"/>
       <c r="K40" s="28" t="s">
         <v>46</v>
       </c>
@@ -2612,28 +2622,28 @@
       <c r="E41" s="1">
         <v>63</v>
       </c>
-      <c r="F41" s="36" t="b">
+      <c r="F41" s="38" t="b">
         <f>AND((B41&lt;=$E$14),(C41&gt;=$E$14),(D41&gt;=$E$3))</f>
         <v>0</v>
       </c>
-      <c r="G41" s="36"/>
-      <c r="H41" s="36">
+      <c r="G41" s="38"/>
+      <c r="H41" s="38">
         <f>IF(F41,$E$3*60000/PI()/E41,0)</f>
         <v>0</v>
       </c>
-      <c r="I41" s="36"/>
-      <c r="J41" s="44"/>
+      <c r="I41" s="38"/>
+      <c r="J41" s="45"/>
       <c r="K41" s="16" t="str">
         <f>IF($H41,L$36/$H41,"-")</f>
         <v>-</v>
       </c>
       <c r="L41" s="8"/>
-      <c r="M41" s="1">
-        <f ca="1">SUMIF($X:$Z,L41,$AE:$AE)-SUMIF($X:$Z,L41,$AF:$AF)</f>
+      <c r="M41" s="58">
+        <f>IF(K41&lt;&gt;"-",SUMIF($AC:$AE,L41,$AJ:$AJ)-K41*SUMIF($AC:$AE,L41,$AK:$AK),0)</f>
         <v>0</v>
       </c>
       <c r="N41" s="8">
-        <f ca="1">M41*N$39</f>
+        <f>M41*N$39</f>
         <v>0</v>
       </c>
       <c r="O41" s="16" t="str">
@@ -2641,12 +2651,12 @@
         <v>-</v>
       </c>
       <c r="P41" s="8"/>
-      <c r="Q41" s="8">
-        <f ca="1">SUMIF($X:$Z,P41,$AC:$AC)</f>
+      <c r="Q41" s="58">
+        <f>IF(O41&lt;&gt;"-",SUMIF($AC:$AE,P41,$AJ:$AJ)-O41*SUMIF($AC:$AE,P41,$AK:$AK),0)</f>
         <v>0</v>
       </c>
       <c r="R41" s="8">
-        <f ca="1">Q41*R$39</f>
+        <f>Q41*R$39</f>
         <v>0</v>
       </c>
       <c r="S41" s="16" t="str">
@@ -2654,12 +2664,12 @@
         <v>-</v>
       </c>
       <c r="T41" s="8"/>
-      <c r="U41" s="8">
-        <f ca="1">SUMIF($X:$Z,T41,$AC:$AC)</f>
+      <c r="U41" s="58">
+        <f>IF(S41&lt;&gt;"-",SUMIF($AC:$AE,T41,$AJ:$AJ)-S41*SUMIF($AC:$AE,T41,$AK:$AK),0)</f>
         <v>0</v>
       </c>
       <c r="V41" s="8">
-        <f ca="1">U41*V$39</f>
+        <f>U41*V$39</f>
         <v>0</v>
       </c>
       <c r="W41" s="16" t="str">
@@ -2667,12 +2677,12 @@
         <v>-</v>
       </c>
       <c r="X41" s="8"/>
-      <c r="Y41" s="8">
-        <f ca="1">SUMIF($X:$Z,X41,$AC:$AC)</f>
+      <c r="Y41" s="58">
+        <f>IF(W41&lt;&gt;"-",SUMIF($AC:$AE,X41,$AJ:$AJ)-W41*SUMIF($AC:$AE,X41,$AK:$AK),0)</f>
         <v>0</v>
       </c>
       <c r="Z41" s="6">
-        <f ca="1">Y41*Z$39</f>
+        <f>Y41*Z$39</f>
         <v>0</v>
       </c>
     </row>
@@ -2689,80 +2699,80 @@
       <c r="E42" s="31">
         <v>83</v>
       </c>
-      <c r="F42" s="36" t="b">
-        <f t="shared" ref="F42:F55" si="3">AND((B42&lt;=$E$14),(C42&gt;=$E$14),(D42&gt;=$E$3))</f>
+      <c r="F42" s="38" t="b">
+        <f t="shared" ref="F42:F55" si="4">AND((B42&lt;=$E$14),(C42&gt;=$E$14),(D42&gt;=$E$3))</f>
         <v>1</v>
       </c>
-      <c r="G42" s="36"/>
-      <c r="H42" s="48">
+      <c r="G42" s="38"/>
+      <c r="H42" s="53">
         <f>IF(F42,$E$3*60000/PI()/E42,0)</f>
         <v>368.16565148968562</v>
       </c>
-      <c r="I42" s="48"/>
-      <c r="J42" s="49"/>
+      <c r="I42" s="53"/>
+      <c r="J42" s="54"/>
       <c r="K42" s="14">
-        <f t="shared" ref="K42:K55" si="4">IF($H42,L$36/$H42,"-")</f>
+        <f t="shared" ref="K42:K55" si="5">IF($H42,L$36/$H42,"-")</f>
         <v>7.8633082371648273</v>
       </c>
       <c r="L42" s="1" t="str">
-        <f>X3</f>
+        <f>AC3</f>
         <v>Прямозубая 1</v>
       </c>
-      <c r="M42" s="1">
-        <f ca="1">SUMIF($X:$Z,L42,$AE:$AE)-SUMIF($X:$Z,L42,$AF:$AF)</f>
-        <v>0</v>
+      <c r="M42" s="35">
+        <f t="shared" ref="M42:M55" ca="1" si="6">IF(K42&lt;&gt;"-",SUMIF($AC:$AE,L42,$AJ:$AJ)-K42*SUMIF($AC:$AE,L42,$AK:$AK),0)</f>
+        <v>0.96042716175885989</v>
       </c>
       <c r="N42" s="1">
-        <f t="shared" ref="N42:N55" ca="1" si="5">M42*N$39</f>
-        <v>2.5591268587500018E-3</v>
+        <f t="shared" ref="N42:N55" ca="1" si="7">M42*N$39</f>
+        <v>0.78651358256964121</v>
       </c>
       <c r="O42" s="30">
-        <f t="shared" ref="O42:O55" si="6">IF($H42,P$36/$H42,"-")</f>
+        <f t="shared" ref="O42:O55" si="8">IF($H42,P$36/$H42,"-")</f>
         <v>3.9112828537192925</v>
       </c>
       <c r="P42" s="31" t="str">
-        <f>X3</f>
+        <f>AC3</f>
         <v>Прямозубая 1</v>
       </c>
-      <c r="Q42" s="31">
-        <f t="shared" ref="Q42:Q55" ca="1" si="7">SUMIF($X:$Z,P42,$AC:$AC)</f>
-        <v>0.97</v>
+      <c r="Q42" s="36">
+        <f t="shared" ref="Q42:Q55" ca="1" si="9">IF(O42&lt;&gt;"-",SUMIF($AC:$AE,P42,$AJ:$AJ)-O42*SUMIF($AC:$AE,P42,$AK:$AK),0)</f>
+        <v>0.97277724108212715</v>
       </c>
       <c r="R42" s="31">
-        <f t="shared" ref="R42:R55" ca="1" si="8">Q42*R$39</f>
-        <v>0.79617907575359981</v>
+        <f t="shared" ref="R42:R55" ca="1" si="10">Q42*R$39</f>
+        <v>0.79845864404010802</v>
       </c>
       <c r="S42" s="14">
-        <f t="shared" ref="S42:S55" si="9">IF($H42,T$36/$H42,"-")</f>
+        <f t="shared" ref="S42:S55" si="11">IF($H42,T$36/$H42,"-")</f>
         <v>2.6075219024795282</v>
       </c>
       <c r="T42" s="1" t="str">
-        <f>X3</f>
+        <f>AC3</f>
         <v>Прямозубая 1</v>
       </c>
-      <c r="U42" s="1">
-        <f t="shared" ref="U42:U55" ca="1" si="10">SUMIF($X:$Z,T42,$AC:$AC)</f>
-        <v>0.97</v>
+      <c r="U42" s="35">
+        <f t="shared" ref="U42:U55" ca="1" si="12">IF(S42&lt;&gt;"-",SUMIF($AC:$AE,T42,$AJ:$AJ)-S42*SUMIF($AC:$AE,T42,$AK:$AK),0)</f>
+        <v>0.97685149405475147</v>
       </c>
       <c r="V42" s="1">
-        <f t="shared" ref="V42:V55" ca="1" si="11">U42*V$39</f>
-        <v>0.7852224829679999</v>
+        <f t="shared" ref="V42:V55" ca="1" si="13">U42*V$39</f>
+        <v>0.790768820260487</v>
       </c>
       <c r="W42" s="14">
-        <f t="shared" ref="W42:W55" si="12">IF($H42,X$36/$H42,"-")</f>
+        <f t="shared" ref="W42:W55" si="14">IF($H42,X$36/$H42,"-")</f>
         <v>1.9746546073985594</v>
       </c>
       <c r="X42" s="1" t="str">
-        <f>X3</f>
+        <f>AC3</f>
         <v>Прямозубая 1</v>
       </c>
-      <c r="Y42" s="1">
-        <f t="shared" ref="Y42:Y55" ca="1" si="13">SUMIF($X:$Z,X42,$AC:$AC)</f>
-        <v>0.97</v>
+      <c r="Y42" s="35">
+        <f t="shared" ref="Y42:Y55" ca="1" si="15">IF(W42&lt;&gt;"-",SUMIF($AC:$AE,X42,$AJ:$AJ)-W42*SUMIF($AC:$AE,X42,$AK:$AK),0)</f>
+        <v>0.97882920435187948</v>
       </c>
       <c r="Z42" s="3">
-        <f t="shared" ref="Z42:Z55" ca="1" si="14">Y42*Z$39</f>
-        <v>0.77609198897999987</v>
+        <f t="shared" ref="Z42:Z55" ca="1" si="16">Y42*Z$39</f>
+        <v>0.78315618977026902</v>
       </c>
     </row>
     <row r="43" spans="2:26" x14ac:dyDescent="0.3">
@@ -2778,79 +2788,79 @@
       <c r="E43" s="1">
         <v>89</v>
       </c>
-      <c r="F43" s="36" t="b">
-        <f t="shared" si="3"/>
+      <c r="F43" s="38" t="b">
+        <f t="shared" si="4"/>
         <v>1</v>
       </c>
-      <c r="G43" s="36"/>
-      <c r="H43" s="36">
-        <f t="shared" ref="H43:H55" si="15">IF(F43,$E$3*60000/PI()/E43,0)</f>
+      <c r="G43" s="38"/>
+      <c r="H43" s="38">
+        <f t="shared" ref="H43:H55" si="17">IF(F43,$E$3*60000/PI()/E43,0)</f>
         <v>343.34549520948212</v>
       </c>
-      <c r="I43" s="36"/>
-      <c r="J43" s="44"/>
+      <c r="I43" s="38"/>
+      <c r="J43" s="45"/>
       <c r="K43" s="14">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>8.4317401579237305</v>
       </c>
       <c r="L43" s="1" t="s">
         <v>112</v>
       </c>
-      <c r="M43" s="1">
-        <f t="shared" ref="M43:M55" ca="1" si="16">SUMIF($X:$Z,L43,$AE:$AE)-SUMIF($X:$Z,L43,$AF:$AF)</f>
+      <c r="M43" s="35">
+        <f t="shared" ca="1" si="6"/>
         <v>0</v>
       </c>
       <c r="N43" s="1">
-        <f t="shared" ca="1" si="5"/>
+        <f t="shared" ca="1" si="7"/>
         <v>0</v>
       </c>
       <c r="O43" s="14">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>4.1940261925423732</v>
       </c>
       <c r="P43" s="1" t="str">
-        <f>X3</f>
+        <f>AC3</f>
         <v>Прямозубая 1</v>
       </c>
-      <c r="Q43" s="1">
-        <f t="shared" ca="1" si="7"/>
-        <v>0.97</v>
+      <c r="Q43" s="35">
+        <f t="shared" ca="1" si="9"/>
+        <v>0.97189366814830502</v>
       </c>
       <c r="R43" s="1">
-        <f t="shared" ca="1" si="8"/>
-        <v>0.79617907575359981</v>
+        <f t="shared" ca="1" si="10"/>
+        <v>0.79773340457432307</v>
       </c>
       <c r="S43" s="14">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>2.7960174616949156</v>
       </c>
       <c r="T43" s="1" t="str">
-        <f>X3</f>
+        <f>AC3</f>
         <v>Прямозубая 1</v>
       </c>
-      <c r="U43" s="1">
-        <f t="shared" ca="1" si="10"/>
-        <v>0.97</v>
+      <c r="U43" s="35">
+        <f t="shared" ca="1" si="12"/>
+        <v>0.97626244543220342</v>
       </c>
       <c r="V43" s="1">
-        <f t="shared" ca="1" si="11"/>
-        <v>0.7852224829679999</v>
+        <f t="shared" ca="1" si="13"/>
+        <v>0.79029198085637764</v>
       </c>
       <c r="W43" s="14">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>2.1174007235960453</v>
       </c>
       <c r="X43" s="1" t="str">
-        <f>X3</f>
+        <f>AC3</f>
         <v>Прямозубая 1</v>
       </c>
-      <c r="Y43" s="1">
-        <f t="shared" ca="1" si="13"/>
-        <v>0.97</v>
+      <c r="Y43" s="35">
+        <f t="shared" ca="1" si="15"/>
+        <v>0.97838312273876238</v>
       </c>
       <c r="Z43" s="3">
-        <f t="shared" ca="1" si="14"/>
-        <v>0.77609198897999987</v>
+        <f t="shared" ca="1" si="16"/>
+        <v>0.78279928217607164</v>
       </c>
     </row>
     <row r="44" spans="2:26" x14ac:dyDescent="0.3">
@@ -2866,67 +2876,67 @@
       <c r="E44" s="1">
         <v>83</v>
       </c>
-      <c r="F44" s="36" t="b">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="G44" s="36"/>
-      <c r="H44" s="36">
+      <c r="F44" s="38" t="b">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="G44" s="38"/>
+      <c r="H44" s="38">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+      <c r="I44" s="38"/>
+      <c r="J44" s="45"/>
+      <c r="K44" s="14" t="str">
+        <f t="shared" si="5"/>
+        <v>-</v>
+      </c>
+      <c r="L44" s="1"/>
+      <c r="M44" s="35">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="N44" s="1">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="O44" s="14" t="str">
+        <f t="shared" si="8"/>
+        <v>-</v>
+      </c>
+      <c r="P44" s="1"/>
+      <c r="Q44" s="35">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="R44" s="1">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="S44" s="14" t="str">
+        <f t="shared" si="11"/>
+        <v>-</v>
+      </c>
+      <c r="T44" s="1"/>
+      <c r="U44" s="35">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="V44" s="1">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+      <c r="W44" s="14" t="str">
+        <f t="shared" si="14"/>
+        <v>-</v>
+      </c>
+      <c r="X44" s="1"/>
+      <c r="Y44" s="35">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
-      <c r="I44" s="36"/>
-      <c r="J44" s="44"/>
-      <c r="K44" s="14" t="str">
-        <f t="shared" si="4"/>
-        <v>-</v>
-      </c>
-      <c r="L44" s="1"/>
-      <c r="M44" s="1">
-        <f t="shared" ca="1" si="16"/>
-        <v>0</v>
-      </c>
-      <c r="N44" s="1">
-        <f t="shared" ca="1" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="O44" s="14" t="str">
-        <f t="shared" si="6"/>
-        <v>-</v>
-      </c>
-      <c r="P44" s="1"/>
-      <c r="Q44" s="1">
-        <f t="shared" ca="1" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="R44" s="1">
-        <f t="shared" ca="1" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="S44" s="14" t="str">
-        <f t="shared" si="9"/>
-        <v>-</v>
-      </c>
-      <c r="T44" s="1"/>
-      <c r="U44" s="1">
-        <f t="shared" ca="1" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="V44" s="1">
-        <f t="shared" ca="1" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="W44" s="14" t="str">
-        <f t="shared" si="12"/>
-        <v>-</v>
-      </c>
-      <c r="X44" s="1"/>
-      <c r="Y44" s="1">
-        <f t="shared" ca="1" si="13"/>
-        <v>0</v>
-      </c>
       <c r="Z44" s="3">
-        <f t="shared" ca="1" si="14"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
     </row>
@@ -2943,67 +2953,67 @@
       <c r="E45" s="1">
         <v>89</v>
       </c>
-      <c r="F45" s="36" t="b">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="G45" s="36"/>
-      <c r="H45" s="36">
+      <c r="F45" s="38" t="b">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="G45" s="38"/>
+      <c r="H45" s="38">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+      <c r="I45" s="38"/>
+      <c r="J45" s="45"/>
+      <c r="K45" s="14" t="str">
+        <f t="shared" si="5"/>
+        <v>-</v>
+      </c>
+      <c r="L45" s="1"/>
+      <c r="M45" s="35">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="N45" s="1">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="O45" s="14" t="str">
+        <f t="shared" si="8"/>
+        <v>-</v>
+      </c>
+      <c r="P45" s="1"/>
+      <c r="Q45" s="35">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="R45" s="1">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="S45" s="14" t="str">
+        <f t="shared" si="11"/>
+        <v>-</v>
+      </c>
+      <c r="T45" s="1"/>
+      <c r="U45" s="35">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="V45" s="1">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+      <c r="W45" s="14" t="str">
+        <f t="shared" si="14"/>
+        <v>-</v>
+      </c>
+      <c r="X45" s="1"/>
+      <c r="Y45" s="35">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
-      <c r="I45" s="36"/>
-      <c r="J45" s="44"/>
-      <c r="K45" s="14" t="str">
-        <f t="shared" si="4"/>
-        <v>-</v>
-      </c>
-      <c r="L45" s="1"/>
-      <c r="M45" s="1">
-        <f t="shared" ca="1" si="16"/>
-        <v>0</v>
-      </c>
-      <c r="N45" s="1">
-        <f t="shared" ca="1" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="O45" s="14" t="str">
-        <f t="shared" si="6"/>
-        <v>-</v>
-      </c>
-      <c r="P45" s="1"/>
-      <c r="Q45" s="1">
-        <f t="shared" ca="1" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="R45" s="1">
-        <f t="shared" ca="1" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="S45" s="14" t="str">
-        <f t="shared" si="9"/>
-        <v>-</v>
-      </c>
-      <c r="T45" s="1"/>
-      <c r="U45" s="1">
-        <f t="shared" ca="1" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="V45" s="1">
-        <f t="shared" ca="1" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="W45" s="14" t="str">
-        <f t="shared" si="12"/>
-        <v>-</v>
-      </c>
-      <c r="X45" s="1"/>
-      <c r="Y45" s="1">
-        <f t="shared" ca="1" si="13"/>
-        <v>0</v>
-      </c>
       <c r="Z45" s="3">
-        <f t="shared" ca="1" si="14"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
     </row>
@@ -3020,79 +3030,79 @@
       <c r="E46" s="1">
         <v>102</v>
       </c>
-      <c r="F46" s="36" t="b">
-        <f t="shared" si="3"/>
+      <c r="F46" s="38" t="b">
+        <f t="shared" si="4"/>
         <v>1</v>
       </c>
-      <c r="G46" s="36"/>
-      <c r="H46" s="36">
-        <f t="shared" si="15"/>
+      <c r="G46" s="38"/>
+      <c r="H46" s="38">
+        <f t="shared" si="17"/>
         <v>299.58577523180298</v>
       </c>
-      <c r="I46" s="36"/>
-      <c r="J46" s="44"/>
+      <c r="I46" s="38"/>
+      <c r="J46" s="45"/>
       <c r="K46" s="14">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>9.6633426529013544</v>
       </c>
       <c r="L46" s="1" t="s">
         <v>112</v>
       </c>
-      <c r="M46" s="1">
+      <c r="M46" s="35">
+        <f t="shared" ca="1" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="N46" s="1">
+        <f t="shared" ca="1" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="O46" s="14">
+        <f t="shared" si="8"/>
+        <v>4.8066367599923838</v>
+      </c>
+      <c r="P46" s="26" t="str">
+        <f>AC3</f>
+        <v>Прямозубая 1</v>
+      </c>
+      <c r="Q46" s="35">
+        <f t="shared" ca="1" si="9"/>
+        <v>0.96997926012502378</v>
+      </c>
+      <c r="R46" s="1">
+        <f t="shared" ca="1" si="10"/>
+        <v>0.79616205239845572</v>
+      </c>
+      <c r="S46" s="14">
+        <f t="shared" si="11"/>
+        <v>3.2044245066615891</v>
+      </c>
+      <c r="T46" s="1" t="str">
+        <f>AC3</f>
+        <v>Прямозубая 1</v>
+      </c>
+      <c r="U46" s="35">
+        <f t="shared" ca="1" si="12"/>
+        <v>0.97498617341668248</v>
+      </c>
+      <c r="V46" s="1">
+        <f t="shared" ca="1" si="13"/>
+        <v>0.78925882881414056</v>
+      </c>
+      <c r="W46" s="14">
+        <f t="shared" si="14"/>
+        <v>2.4266839753572658</v>
+      </c>
+      <c r="X46" s="1" t="str">
+        <f>AC3</f>
+        <v>Прямозубая 1</v>
+      </c>
+      <c r="Y46" s="35">
+        <f t="shared" ca="1" si="15"/>
+        <v>0.97741661257700851</v>
+      </c>
+      <c r="Z46" s="3">
         <f t="shared" ca="1" si="16"/>
-        <v>0</v>
-      </c>
-      <c r="N46" s="1">
-        <f t="shared" ca="1" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="O46" s="14">
-        <f t="shared" si="6"/>
-        <v>4.8066367599923838</v>
-      </c>
-      <c r="P46" s="26" t="str">
-        <f>X3</f>
-        <v>Прямозубая 1</v>
-      </c>
-      <c r="Q46" s="1">
-        <f t="shared" ca="1" si="7"/>
-        <v>0.97</v>
-      </c>
-      <c r="R46" s="1">
-        <f t="shared" ca="1" si="8"/>
-        <v>0.79617907575359981</v>
-      </c>
-      <c r="S46" s="14">
-        <f t="shared" si="9"/>
-        <v>3.2044245066615891</v>
-      </c>
-      <c r="T46" s="1" t="str">
-        <f>X3</f>
-        <v>Прямозубая 1</v>
-      </c>
-      <c r="U46" s="1">
-        <f t="shared" ca="1" si="10"/>
-        <v>0.97</v>
-      </c>
-      <c r="V46" s="1">
-        <f t="shared" ca="1" si="11"/>
-        <v>0.7852224829679999</v>
-      </c>
-      <c r="W46" s="14">
-        <f t="shared" si="12"/>
-        <v>2.4266839753572658</v>
-      </c>
-      <c r="X46" s="1" t="str">
-        <f>X3</f>
-        <v>Прямозубая 1</v>
-      </c>
-      <c r="Y46" s="1">
-        <f t="shared" ca="1" si="13"/>
-        <v>0.97</v>
-      </c>
-      <c r="Z46" s="3">
-        <f t="shared" ca="1" si="14"/>
-        <v>0.77609198897999987</v>
+        <v>0.78202598238864385</v>
       </c>
     </row>
     <row r="47" spans="2:26" x14ac:dyDescent="0.3">
@@ -3108,79 +3118,79 @@
       <c r="E47" s="1">
         <v>108</v>
       </c>
-      <c r="F47" s="36" t="b">
-        <f t="shared" si="3"/>
+      <c r="F47" s="38" t="b">
+        <f t="shared" si="4"/>
         <v>1</v>
       </c>
-      <c r="G47" s="36"/>
-      <c r="H47" s="36">
-        <f t="shared" si="15"/>
+      <c r="G47" s="38"/>
+      <c r="H47" s="38">
+        <f t="shared" si="17"/>
         <v>282.94212105225841</v>
       </c>
-      <c r="I47" s="36"/>
-      <c r="J47" s="44"/>
+      <c r="I47" s="38"/>
+      <c r="J47" s="45"/>
       <c r="K47" s="14">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>10.231774573660257</v>
       </c>
       <c r="L47" s="1" t="s">
         <v>112</v>
       </c>
-      <c r="M47" s="1">
+      <c r="M47" s="35">
+        <f t="shared" ca="1" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="N47" s="1">
+        <f t="shared" ca="1" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="O47" s="14">
+        <f t="shared" si="8"/>
+        <v>5.0893800988154645</v>
+      </c>
+      <c r="P47" s="1" t="str">
+        <f>AC3</f>
+        <v>Прямозубая 1</v>
+      </c>
+      <c r="Q47" s="35">
+        <f t="shared" ca="1" si="9"/>
+        <v>0.96909568719120165</v>
+      </c>
+      <c r="R47" s="1">
+        <f t="shared" ca="1" si="10"/>
+        <v>0.79543681293267077</v>
+      </c>
+      <c r="S47" s="14">
+        <f t="shared" si="11"/>
+        <v>3.392920065876976</v>
+      </c>
+      <c r="T47" s="1" t="str">
+        <f>AC3</f>
+        <v>Прямозубая 1</v>
+      </c>
+      <c r="U47" s="35">
+        <f t="shared" ca="1" si="12"/>
+        <v>0.97439712479413443</v>
+      </c>
+      <c r="V47" s="1">
+        <f t="shared" ca="1" si="13"/>
+        <v>0.78878198941003119</v>
+      </c>
+      <c r="W47" s="14">
+        <f t="shared" si="14"/>
+        <v>2.5694300915547519</v>
+      </c>
+      <c r="X47" s="1" t="str">
+        <f>AC3</f>
+        <v>Прямозубая 1</v>
+      </c>
+      <c r="Y47" s="35">
+        <f t="shared" ca="1" si="15"/>
+        <v>0.97697053096389141</v>
+      </c>
+      <c r="Z47" s="3">
         <f t="shared" ca="1" si="16"/>
-        <v>0</v>
-      </c>
-      <c r="N47" s="1">
-        <f t="shared" ca="1" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="O47" s="14">
-        <f t="shared" si="6"/>
-        <v>5.0893800988154645</v>
-      </c>
-      <c r="P47" s="1" t="str">
-        <f>X3</f>
-        <v>Прямозубая 1</v>
-      </c>
-      <c r="Q47" s="1">
-        <f t="shared" ca="1" si="7"/>
-        <v>0.97</v>
-      </c>
-      <c r="R47" s="1">
-        <f t="shared" ca="1" si="8"/>
-        <v>0.79617907575359981</v>
-      </c>
-      <c r="S47" s="14">
-        <f t="shared" si="9"/>
-        <v>3.392920065876976</v>
-      </c>
-      <c r="T47" s="1" t="str">
-        <f>X3</f>
-        <v>Прямозубая 1</v>
-      </c>
-      <c r="U47" s="1">
-        <f t="shared" ca="1" si="10"/>
-        <v>0.97</v>
-      </c>
-      <c r="V47" s="1">
-        <f t="shared" ca="1" si="11"/>
-        <v>0.7852224829679999</v>
-      </c>
-      <c r="W47" s="14">
-        <f t="shared" si="12"/>
-        <v>2.5694300915547519</v>
-      </c>
-      <c r="X47" s="1" t="str">
-        <f>X3</f>
-        <v>Прямозубая 1</v>
-      </c>
-      <c r="Y47" s="1">
-        <f t="shared" ca="1" si="13"/>
-        <v>0.97</v>
-      </c>
-      <c r="Z47" s="3">
-        <f t="shared" ca="1" si="14"/>
-        <v>0.77609198897999987</v>
+        <v>0.78166907479444647</v>
       </c>
     </row>
     <row r="48" spans="2:26" x14ac:dyDescent="0.3">
@@ -3196,67 +3206,67 @@
       <c r="E48" s="1">
         <v>127</v>
       </c>
-      <c r="F48" s="36" t="b">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="G48" s="36"/>
-      <c r="H48" s="36">
+      <c r="F48" s="38" t="b">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="G48" s="38"/>
+      <c r="H48" s="38">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+      <c r="I48" s="38"/>
+      <c r="J48" s="45"/>
+      <c r="K48" s="14" t="str">
+        <f t="shared" si="5"/>
+        <v>-</v>
+      </c>
+      <c r="L48" s="1"/>
+      <c r="M48" s="35">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="N48" s="1">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="O48" s="14" t="str">
+        <f t="shared" si="8"/>
+        <v>-</v>
+      </c>
+      <c r="P48" s="1"/>
+      <c r="Q48" s="35">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="R48" s="1">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="S48" s="14" t="str">
+        <f t="shared" si="11"/>
+        <v>-</v>
+      </c>
+      <c r="T48" s="1"/>
+      <c r="U48" s="35">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="V48" s="1">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+      <c r="W48" s="14" t="str">
+        <f t="shared" si="14"/>
+        <v>-</v>
+      </c>
+      <c r="X48" s="1"/>
+      <c r="Y48" s="35">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
-      <c r="I48" s="36"/>
-      <c r="J48" s="44"/>
-      <c r="K48" s="14" t="str">
-        <f t="shared" si="4"/>
-        <v>-</v>
-      </c>
-      <c r="L48" s="1"/>
-      <c r="M48" s="1">
-        <f t="shared" ca="1" si="16"/>
-        <v>0</v>
-      </c>
-      <c r="N48" s="1">
-        <f t="shared" ca="1" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="O48" s="14" t="str">
-        <f t="shared" si="6"/>
-        <v>-</v>
-      </c>
-      <c r="P48" s="1"/>
-      <c r="Q48" s="1">
-        <f t="shared" ca="1" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="R48" s="1">
-        <f t="shared" ca="1" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="S48" s="14" t="str">
-        <f t="shared" si="9"/>
-        <v>-</v>
-      </c>
-      <c r="T48" s="1"/>
-      <c r="U48" s="1">
-        <f t="shared" ca="1" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="V48" s="1">
-        <f t="shared" ca="1" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="W48" s="14" t="str">
-        <f t="shared" si="12"/>
-        <v>-</v>
-      </c>
-      <c r="X48" s="1"/>
-      <c r="Y48" s="1">
-        <f t="shared" ca="1" si="13"/>
-        <v>0</v>
-      </c>
       <c r="Z48" s="3">
-        <f t="shared" ca="1" si="14"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
     </row>
@@ -3273,67 +3283,67 @@
       <c r="E49" s="1">
         <v>133</v>
       </c>
-      <c r="F49" s="36" t="b">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="G49" s="36"/>
-      <c r="H49" s="36">
+      <c r="F49" s="38" t="b">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="G49" s="38"/>
+      <c r="H49" s="38">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+      <c r="I49" s="38"/>
+      <c r="J49" s="45"/>
+      <c r="K49" s="14" t="str">
+        <f t="shared" si="5"/>
+        <v>-</v>
+      </c>
+      <c r="L49" s="1"/>
+      <c r="M49" s="35">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="N49" s="1">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="O49" s="14" t="str">
+        <f t="shared" si="8"/>
+        <v>-</v>
+      </c>
+      <c r="P49" s="1"/>
+      <c r="Q49" s="35">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="R49" s="1">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="S49" s="14" t="str">
+        <f t="shared" si="11"/>
+        <v>-</v>
+      </c>
+      <c r="T49" s="1"/>
+      <c r="U49" s="35">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="V49" s="1">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+      <c r="W49" s="14" t="str">
+        <f t="shared" si="14"/>
+        <v>-</v>
+      </c>
+      <c r="X49" s="1"/>
+      <c r="Y49" s="35">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
-      <c r="I49" s="36"/>
-      <c r="J49" s="44"/>
-      <c r="K49" s="14" t="str">
-        <f t="shared" si="4"/>
-        <v>-</v>
-      </c>
-      <c r="L49" s="1"/>
-      <c r="M49" s="1">
-        <f t="shared" ca="1" si="16"/>
-        <v>0</v>
-      </c>
-      <c r="N49" s="1">
-        <f t="shared" ca="1" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="O49" s="14" t="str">
-        <f t="shared" si="6"/>
-        <v>-</v>
-      </c>
-      <c r="P49" s="1"/>
-      <c r="Q49" s="1">
-        <f t="shared" ca="1" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="R49" s="1">
-        <f t="shared" ca="1" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="S49" s="14" t="str">
-        <f t="shared" si="9"/>
-        <v>-</v>
-      </c>
-      <c r="T49" s="1"/>
-      <c r="U49" s="1">
-        <f t="shared" ca="1" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="V49" s="1">
-        <f t="shared" ca="1" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="W49" s="14" t="str">
-        <f t="shared" si="12"/>
-        <v>-</v>
-      </c>
-      <c r="X49" s="1"/>
-      <c r="Y49" s="1">
-        <f t="shared" ca="1" si="13"/>
-        <v>0</v>
-      </c>
       <c r="Z49" s="3">
-        <f t="shared" ca="1" si="14"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
     </row>
@@ -3350,67 +3360,67 @@
       <c r="E50" s="1">
         <v>152</v>
       </c>
-      <c r="F50" s="36" t="b">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="G50" s="36"/>
-      <c r="H50" s="36">
+      <c r="F50" s="38" t="b">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="G50" s="38"/>
+      <c r="H50" s="38">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+      <c r="I50" s="38"/>
+      <c r="J50" s="45"/>
+      <c r="K50" s="14" t="str">
+        <f t="shared" si="5"/>
+        <v>-</v>
+      </c>
+      <c r="L50" s="1"/>
+      <c r="M50" s="35">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="N50" s="1">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="O50" s="14" t="str">
+        <f t="shared" si="8"/>
+        <v>-</v>
+      </c>
+      <c r="P50" s="1"/>
+      <c r="Q50" s="35">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="R50" s="1">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="S50" s="14" t="str">
+        <f t="shared" si="11"/>
+        <v>-</v>
+      </c>
+      <c r="T50" s="1"/>
+      <c r="U50" s="35">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="V50" s="1">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+      <c r="W50" s="14" t="str">
+        <f t="shared" si="14"/>
+        <v>-</v>
+      </c>
+      <c r="X50" s="1"/>
+      <c r="Y50" s="35">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
-      <c r="I50" s="36"/>
-      <c r="J50" s="44"/>
-      <c r="K50" s="14" t="str">
-        <f t="shared" si="4"/>
-        <v>-</v>
-      </c>
-      <c r="L50" s="1"/>
-      <c r="M50" s="1">
-        <f t="shared" ca="1" si="16"/>
-        <v>0</v>
-      </c>
-      <c r="N50" s="1">
-        <f t="shared" ca="1" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="O50" s="14" t="str">
-        <f t="shared" si="6"/>
-        <v>-</v>
-      </c>
-      <c r="P50" s="1"/>
-      <c r="Q50" s="1">
-        <f t="shared" ca="1" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="R50" s="1">
-        <f t="shared" ca="1" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="S50" s="14" t="str">
-        <f t="shared" si="9"/>
-        <v>-</v>
-      </c>
-      <c r="T50" s="1"/>
-      <c r="U50" s="1">
-        <f t="shared" ca="1" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="V50" s="1">
-        <f t="shared" ca="1" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="W50" s="14" t="str">
-        <f t="shared" si="12"/>
-        <v>-</v>
-      </c>
-      <c r="X50" s="1"/>
-      <c r="Y50" s="1">
-        <f t="shared" ca="1" si="13"/>
-        <v>0</v>
-      </c>
       <c r="Z50" s="3">
-        <f t="shared" ca="1" si="14"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
     </row>
@@ -3427,67 +3437,67 @@
       <c r="E51" s="1">
         <v>159</v>
       </c>
-      <c r="F51" s="36" t="b">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="G51" s="36"/>
-      <c r="H51" s="36">
+      <c r="F51" s="38" t="b">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="G51" s="38"/>
+      <c r="H51" s="38">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+      <c r="I51" s="38"/>
+      <c r="J51" s="45"/>
+      <c r="K51" s="14" t="str">
+        <f t="shared" si="5"/>
+        <v>-</v>
+      </c>
+      <c r="L51" s="1"/>
+      <c r="M51" s="35">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="N51" s="1">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="O51" s="14" t="str">
+        <f t="shared" si="8"/>
+        <v>-</v>
+      </c>
+      <c r="P51" s="1"/>
+      <c r="Q51" s="35">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="R51" s="1">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="S51" s="14" t="str">
+        <f t="shared" si="11"/>
+        <v>-</v>
+      </c>
+      <c r="T51" s="1"/>
+      <c r="U51" s="35">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="V51" s="1">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+      <c r="W51" s="14" t="str">
+        <f t="shared" si="14"/>
+        <v>-</v>
+      </c>
+      <c r="X51" s="1"/>
+      <c r="Y51" s="35">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
-      <c r="I51" s="36"/>
-      <c r="J51" s="44"/>
-      <c r="K51" s="14" t="str">
-        <f t="shared" si="4"/>
-        <v>-</v>
-      </c>
-      <c r="L51" s="1"/>
-      <c r="M51" s="1">
-        <f t="shared" ca="1" si="16"/>
-        <v>0</v>
-      </c>
-      <c r="N51" s="1">
-        <f t="shared" ca="1" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="O51" s="14" t="str">
-        <f t="shared" si="6"/>
-        <v>-</v>
-      </c>
-      <c r="P51" s="1"/>
-      <c r="Q51" s="1">
-        <f t="shared" ca="1" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="R51" s="1">
-        <f t="shared" ca="1" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="S51" s="14" t="str">
-        <f t="shared" si="9"/>
-        <v>-</v>
-      </c>
-      <c r="T51" s="1"/>
-      <c r="U51" s="1">
-        <f t="shared" ca="1" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="V51" s="1">
-        <f t="shared" ca="1" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="W51" s="14" t="str">
-        <f t="shared" si="12"/>
-        <v>-</v>
-      </c>
-      <c r="X51" s="1"/>
-      <c r="Y51" s="1">
-        <f t="shared" ca="1" si="13"/>
-        <v>0</v>
-      </c>
       <c r="Z51" s="3">
-        <f t="shared" ca="1" si="14"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
     </row>
@@ -3504,67 +3514,67 @@
       <c r="E52" s="1">
         <v>152</v>
       </c>
-      <c r="F52" s="36" t="b">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="G52" s="36"/>
-      <c r="H52" s="36">
+      <c r="F52" s="38" t="b">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="G52" s="38"/>
+      <c r="H52" s="38">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+      <c r="I52" s="38"/>
+      <c r="J52" s="45"/>
+      <c r="K52" s="14" t="str">
+        <f t="shared" si="5"/>
+        <v>-</v>
+      </c>
+      <c r="L52" s="1"/>
+      <c r="M52" s="35">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="N52" s="1">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="O52" s="14" t="str">
+        <f t="shared" si="8"/>
+        <v>-</v>
+      </c>
+      <c r="P52" s="1"/>
+      <c r="Q52" s="35">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="R52" s="1">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="S52" s="14" t="str">
+        <f t="shared" si="11"/>
+        <v>-</v>
+      </c>
+      <c r="T52" s="1"/>
+      <c r="U52" s="35">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="V52" s="1">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+      <c r="W52" s="14" t="str">
+        <f t="shared" si="14"/>
+        <v>-</v>
+      </c>
+      <c r="X52" s="1"/>
+      <c r="Y52" s="35">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
-      <c r="I52" s="36"/>
-      <c r="J52" s="44"/>
-      <c r="K52" s="14" t="str">
-        <f t="shared" si="4"/>
-        <v>-</v>
-      </c>
-      <c r="L52" s="1"/>
-      <c r="M52" s="1">
-        <f t="shared" ca="1" si="16"/>
-        <v>0</v>
-      </c>
-      <c r="N52" s="1">
-        <f t="shared" ca="1" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="O52" s="14" t="str">
-        <f t="shared" si="6"/>
-        <v>-</v>
-      </c>
-      <c r="P52" s="1"/>
-      <c r="Q52" s="1">
-        <f t="shared" ca="1" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="R52" s="1">
-        <f t="shared" ca="1" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="S52" s="14" t="str">
-        <f t="shared" si="9"/>
-        <v>-</v>
-      </c>
-      <c r="T52" s="1"/>
-      <c r="U52" s="1">
-        <f t="shared" ca="1" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="V52" s="1">
-        <f t="shared" ca="1" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="W52" s="14" t="str">
-        <f t="shared" si="12"/>
-        <v>-</v>
-      </c>
-      <c r="X52" s="1"/>
-      <c r="Y52" s="1">
-        <f t="shared" ca="1" si="13"/>
-        <v>0</v>
-      </c>
       <c r="Z52" s="3">
-        <f t="shared" ca="1" si="14"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
     </row>
@@ -3581,67 +3591,67 @@
       <c r="E53" s="1">
         <v>159</v>
       </c>
-      <c r="F53" s="36" t="b">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="G53" s="36"/>
-      <c r="H53" s="36">
+      <c r="F53" s="38" t="b">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="G53" s="38"/>
+      <c r="H53" s="38">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+      <c r="I53" s="38"/>
+      <c r="J53" s="45"/>
+      <c r="K53" s="14" t="str">
+        <f t="shared" si="5"/>
+        <v>-</v>
+      </c>
+      <c r="L53" s="1"/>
+      <c r="M53" s="35">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="N53" s="1">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="O53" s="14" t="str">
+        <f t="shared" si="8"/>
+        <v>-</v>
+      </c>
+      <c r="P53" s="1"/>
+      <c r="Q53" s="35">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="R53" s="1">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="S53" s="14" t="str">
+        <f t="shared" si="11"/>
+        <v>-</v>
+      </c>
+      <c r="T53" s="1"/>
+      <c r="U53" s="35">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="V53" s="1">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+      <c r="W53" s="14" t="str">
+        <f t="shared" si="14"/>
+        <v>-</v>
+      </c>
+      <c r="X53" s="1"/>
+      <c r="Y53" s="35">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
-      <c r="I53" s="36"/>
-      <c r="J53" s="44"/>
-      <c r="K53" s="14" t="str">
-        <f t="shared" si="4"/>
-        <v>-</v>
-      </c>
-      <c r="L53" s="1"/>
-      <c r="M53" s="1">
-        <f t="shared" ca="1" si="16"/>
-        <v>0</v>
-      </c>
-      <c r="N53" s="1">
-        <f t="shared" ca="1" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="O53" s="14" t="str">
-        <f t="shared" si="6"/>
-        <v>-</v>
-      </c>
-      <c r="P53" s="1"/>
-      <c r="Q53" s="1">
-        <f t="shared" ca="1" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="R53" s="1">
-        <f t="shared" ca="1" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="S53" s="14" t="str">
-        <f t="shared" si="9"/>
-        <v>-</v>
-      </c>
-      <c r="T53" s="1"/>
-      <c r="U53" s="1">
-        <f t="shared" ca="1" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="V53" s="1">
-        <f t="shared" ca="1" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="W53" s="14" t="str">
-        <f t="shared" si="12"/>
-        <v>-</v>
-      </c>
-      <c r="X53" s="1"/>
-      <c r="Y53" s="1">
-        <f t="shared" ca="1" si="13"/>
-        <v>0</v>
-      </c>
       <c r="Z53" s="3">
-        <f t="shared" ca="1" si="14"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
     </row>
@@ -3658,67 +3668,67 @@
       <c r="E54" s="1">
         <v>152</v>
       </c>
-      <c r="F54" s="36" t="b">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="G54" s="36"/>
-      <c r="H54" s="36">
+      <c r="F54" s="38" t="b">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="G54" s="38"/>
+      <c r="H54" s="38">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+      <c r="I54" s="38"/>
+      <c r="J54" s="45"/>
+      <c r="K54" s="14" t="str">
+        <f t="shared" si="5"/>
+        <v>-</v>
+      </c>
+      <c r="L54" s="1"/>
+      <c r="M54" s="35">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="N54" s="1">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="O54" s="14" t="str">
+        <f t="shared" si="8"/>
+        <v>-</v>
+      </c>
+      <c r="P54" s="1"/>
+      <c r="Q54" s="35">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="R54" s="1">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="S54" s="14" t="str">
+        <f t="shared" si="11"/>
+        <v>-</v>
+      </c>
+      <c r="T54" s="1"/>
+      <c r="U54" s="35">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="V54" s="1">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+      <c r="W54" s="14" t="str">
+        <f t="shared" si="14"/>
+        <v>-</v>
+      </c>
+      <c r="X54" s="1"/>
+      <c r="Y54" s="35">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
-      <c r="I54" s="36"/>
-      <c r="J54" s="44"/>
-      <c r="K54" s="14" t="str">
-        <f t="shared" si="4"/>
-        <v>-</v>
-      </c>
-      <c r="L54" s="1"/>
-      <c r="M54" s="1">
-        <f t="shared" ca="1" si="16"/>
-        <v>0</v>
-      </c>
-      <c r="N54" s="1">
-        <f t="shared" ca="1" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="O54" s="14" t="str">
-        <f t="shared" si="6"/>
-        <v>-</v>
-      </c>
-      <c r="P54" s="1"/>
-      <c r="Q54" s="1">
-        <f t="shared" ca="1" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="R54" s="1">
-        <f t="shared" ca="1" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="S54" s="14" t="str">
-        <f t="shared" si="9"/>
-        <v>-</v>
-      </c>
-      <c r="T54" s="1"/>
-      <c r="U54" s="1">
-        <f t="shared" ca="1" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="V54" s="1">
-        <f t="shared" ca="1" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="W54" s="14" t="str">
-        <f t="shared" si="12"/>
-        <v>-</v>
-      </c>
-      <c r="X54" s="1"/>
-      <c r="Y54" s="1">
-        <f t="shared" ca="1" si="13"/>
-        <v>0</v>
-      </c>
       <c r="Z54" s="3">
-        <f t="shared" ca="1" si="14"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
     </row>
@@ -3735,101 +3745,101 @@
       <c r="E55" s="4">
         <v>159</v>
       </c>
-      <c r="F55" s="38" t="b">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="G55" s="38"/>
-      <c r="H55" s="38">
+      <c r="F55" s="41" t="b">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="G55" s="41"/>
+      <c r="H55" s="41">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+      <c r="I55" s="41"/>
+      <c r="J55" s="46"/>
+      <c r="K55" s="15" t="str">
+        <f t="shared" si="5"/>
+        <v>-</v>
+      </c>
+      <c r="L55" s="4"/>
+      <c r="M55" s="59">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="N55" s="4">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="O55" s="15" t="str">
+        <f t="shared" si="8"/>
+        <v>-</v>
+      </c>
+      <c r="P55" s="4"/>
+      <c r="Q55" s="59">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="R55" s="4">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="S55" s="15" t="str">
+        <f t="shared" si="11"/>
+        <v>-</v>
+      </c>
+      <c r="T55" s="4"/>
+      <c r="U55" s="59">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="V55" s="4">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+      <c r="W55" s="15" t="str">
+        <f t="shared" si="14"/>
+        <v>-</v>
+      </c>
+      <c r="X55" s="4"/>
+      <c r="Y55" s="59">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
-      <c r="I55" s="38"/>
-      <c r="J55" s="52"/>
-      <c r="K55" s="15" t="str">
-        <f t="shared" si="4"/>
-        <v>-</v>
-      </c>
-      <c r="L55" s="4"/>
-      <c r="M55" s="1">
-        <f t="shared" ca="1" si="16"/>
-        <v>0</v>
-      </c>
-      <c r="N55" s="4">
-        <f t="shared" ca="1" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="O55" s="15" t="str">
-        <f t="shared" si="6"/>
-        <v>-</v>
-      </c>
-      <c r="P55" s="4"/>
-      <c r="Q55" s="4">
-        <f t="shared" ca="1" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="R55" s="4">
-        <f t="shared" ca="1" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="S55" s="15" t="str">
-        <f t="shared" si="9"/>
-        <v>-</v>
-      </c>
-      <c r="T55" s="4"/>
-      <c r="U55" s="4">
-        <f t="shared" ca="1" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="V55" s="4">
-        <f t="shared" ca="1" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="W55" s="15" t="str">
-        <f t="shared" si="12"/>
-        <v>-</v>
-      </c>
-      <c r="X55" s="4"/>
-      <c r="Y55" s="4">
-        <f t="shared" ca="1" si="13"/>
-        <v>0</v>
-      </c>
       <c r="Z55" s="5">
-        <f t="shared" ca="1" si="14"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
     </row>
     <row r="56" spans="2:26" x14ac:dyDescent="0.3">
-      <c r="L56" s="36" t="s">
+      <c r="L56" s="38" t="s">
         <v>63</v>
       </c>
-      <c r="M56" s="36"/>
+      <c r="M56" s="38"/>
       <c r="N56" s="32">
         <f ca="1">MAX(Z41:Z55,V41:V55,R41:R55,N41:N55)</f>
-        <v>0.79617907575359981</v>
+        <v>0.79845864404010802</v>
       </c>
     </row>
     <row r="57" spans="2:26" x14ac:dyDescent="0.3">
-      <c r="B57" s="41" t="s">
+      <c r="B57" s="42" t="s">
         <v>121</v>
       </c>
-      <c r="C57" s="39"/>
-      <c r="D57" s="39"/>
-      <c r="E57" s="39"/>
-      <c r="F57" s="39" t="str">
+      <c r="C57" s="43"/>
+      <c r="D57" s="43"/>
+      <c r="E57" s="43"/>
+      <c r="F57" s="43" t="str">
         <f>P46</f>
         <v>Прямозубая 1</v>
       </c>
-      <c r="G57" s="40"/>
+      <c r="G57" s="44"/>
     </row>
     <row r="58" spans="2:26" x14ac:dyDescent="0.3">
-      <c r="B58" s="35" t="s">
+      <c r="B58" s="39" t="s">
         <v>46</v>
       </c>
-      <c r="C58" s="36"/>
-      <c r="D58" s="36"/>
-      <c r="E58" s="36"/>
-      <c r="F58" s="34">
+      <c r="C58" s="38"/>
+      <c r="D58" s="38"/>
+      <c r="E58" s="38"/>
+      <c r="F58" s="33">
         <f>O42</f>
         <v>3.9112828537192925</v>
       </c>
@@ -3854,12 +3864,12 @@
       </c>
     </row>
     <row r="59" spans="2:26" x14ac:dyDescent="0.3">
-      <c r="B59" s="35" t="s">
+      <c r="B59" s="39" t="s">
         <v>106</v>
       </c>
-      <c r="C59" s="36"/>
-      <c r="D59" s="36"/>
-      <c r="E59" s="36"/>
+      <c r="C59" s="38"/>
+      <c r="D59" s="38"/>
+      <c r="E59" s="38"/>
       <c r="F59" s="17">
         <f>P36</f>
         <v>1440</v>
@@ -3883,7 +3893,7 @@
         <v>0.99</v>
       </c>
       <c r="S59">
-        <f>AE3</f>
+        <f>AJ3</f>
         <v>0.98499999999999999</v>
       </c>
       <c r="T59">
@@ -3896,12 +3906,12 @@
       </c>
     </row>
     <row r="60" spans="2:26" x14ac:dyDescent="0.3">
-      <c r="B60" s="35" t="s">
+      <c r="B60" s="39" t="s">
         <v>115</v>
       </c>
-      <c r="C60" s="36"/>
-      <c r="D60" s="36"/>
-      <c r="E60" s="36"/>
+      <c r="C60" s="38"/>
+      <c r="D60" s="38"/>
+      <c r="E60" s="38"/>
       <c r="F60" s="1">
         <f>F59*PI()/30</f>
         <v>150.79644737231007</v>
@@ -3911,12 +3921,12 @@
       </c>
     </row>
     <row r="61" spans="2:26" x14ac:dyDescent="0.3">
-      <c r="B61" s="35" t="s">
+      <c r="B61" s="39" t="s">
         <v>47</v>
       </c>
-      <c r="C61" s="36"/>
-      <c r="D61" s="36"/>
-      <c r="E61" s="36"/>
+      <c r="C61" s="38"/>
+      <c r="D61" s="38"/>
+      <c r="E61" s="38"/>
       <c r="F61" s="17">
         <f>H42</f>
         <v>368.16565148968562</v>
@@ -3926,12 +3936,12 @@
       </c>
     </row>
     <row r="62" spans="2:26" x14ac:dyDescent="0.3">
-      <c r="B62" s="35" t="s">
+      <c r="B62" s="39" t="s">
         <v>118</v>
       </c>
-      <c r="C62" s="36"/>
-      <c r="D62" s="36"/>
-      <c r="E62" s="36"/>
+      <c r="C62" s="38"/>
+      <c r="D62" s="38"/>
+      <c r="E62" s="38"/>
       <c r="F62" s="17">
         <f>E42</f>
         <v>83</v>
@@ -3941,12 +3951,12 @@
       </c>
     </row>
     <row r="63" spans="2:26" x14ac:dyDescent="0.3">
-      <c r="B63" s="35" t="s">
+      <c r="B63" s="39" t="s">
         <v>107</v>
       </c>
-      <c r="C63" s="36"/>
-      <c r="D63" s="36"/>
-      <c r="E63" s="36"/>
+      <c r="C63" s="38"/>
+      <c r="D63" s="38"/>
+      <c r="E63" s="38"/>
       <c r="F63" s="1">
         <f>E2*F62/2</f>
         <v>166</v>
@@ -3956,12 +3966,12 @@
       </c>
     </row>
     <row r="64" spans="2:26" x14ac:dyDescent="0.3">
-      <c r="B64" s="35" t="s">
+      <c r="B64" s="39" t="s">
         <v>108</v>
       </c>
-      <c r="C64" s="36"/>
-      <c r="D64" s="36"/>
-      <c r="E64" s="36"/>
+      <c r="C64" s="38"/>
+      <c r="D64" s="38"/>
+      <c r="E64" s="38"/>
       <c r="F64" s="1">
         <f>F63/F68/F58</f>
         <v>45.775183383347823</v>
@@ -3971,12 +3981,12 @@
       </c>
     </row>
     <row r="65" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B65" s="35" t="s">
+      <c r="B65" s="39" t="s">
         <v>109</v>
       </c>
-      <c r="C65" s="36"/>
-      <c r="D65" s="36"/>
-      <c r="E65" s="36"/>
+      <c r="C65" s="38"/>
+      <c r="D65" s="38"/>
+      <c r="E65" s="38"/>
       <c r="F65" s="1">
         <f>F64*F60/1000</f>
         <v>6.9027350320248528</v>
@@ -3986,12 +3996,12 @@
       </c>
     </row>
     <row r="66" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B66" s="35" t="s">
+      <c r="B66" s="39" t="s">
         <v>113</v>
       </c>
-      <c r="C66" s="36"/>
-      <c r="D66" s="36"/>
-      <c r="E66" s="36"/>
+      <c r="C66" s="38"/>
+      <c r="D66" s="38"/>
+      <c r="E66" s="38"/>
       <c r="F66" s="1">
         <f>Q36</f>
         <v>2.2000000000000002</v>
@@ -3999,12 +4009,12 @@
       <c r="G66" s="3"/>
     </row>
     <row r="67" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B67" s="35" t="s">
+      <c r="B67" s="39" t="s">
         <v>114</v>
       </c>
-      <c r="C67" s="36"/>
-      <c r="D67" s="36"/>
-      <c r="E67" s="36"/>
+      <c r="C67" s="38"/>
+      <c r="D67" s="38"/>
+      <c r="E67" s="38"/>
       <c r="F67" s="1">
         <f>MAX(F66,E8)</f>
         <v>2.2000000000000002</v>
@@ -4012,12 +4022,12 @@
       <c r="G67" s="3"/>
     </row>
     <row r="68" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B68" s="35" t="s">
+      <c r="B68" s="39" t="s">
         <v>120</v>
       </c>
-      <c r="C68" s="36"/>
-      <c r="D68" s="36"/>
-      <c r="E68" s="36"/>
+      <c r="C68" s="38"/>
+      <c r="D68" s="38"/>
+      <c r="E68" s="38"/>
       <c r="F68" s="1">
         <f>U59*S59*T59*R59*Q59</f>
         <v>0.9271687193999999</v>
@@ -4025,12 +4035,12 @@
       <c r="G68" s="3"/>
     </row>
     <row r="69" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B69" s="37" t="s">
+      <c r="B69" s="40" t="s">
         <v>122</v>
       </c>
-      <c r="C69" s="38"/>
-      <c r="D69" s="38"/>
-      <c r="E69" s="38"/>
+      <c r="C69" s="41"/>
+      <c r="D69" s="41"/>
+      <c r="E69" s="41"/>
       <c r="F69" s="4">
         <f>F68*P59</f>
         <v>0.80849112331679995</v>
@@ -4039,109 +4049,9 @@
     </row>
   </sheetData>
   <mergeCells count="130">
-    <mergeCell ref="S19:V19"/>
-    <mergeCell ref="W19:Z19"/>
-    <mergeCell ref="L56:M56"/>
-    <mergeCell ref="I31:J31"/>
-    <mergeCell ref="I32:J32"/>
-    <mergeCell ref="I33:J33"/>
-    <mergeCell ref="I34:J34"/>
-    <mergeCell ref="I35:J35"/>
-    <mergeCell ref="K19:N19"/>
-    <mergeCell ref="I20:J20"/>
-    <mergeCell ref="I21:J21"/>
-    <mergeCell ref="I22:J22"/>
-    <mergeCell ref="I23:J23"/>
-    <mergeCell ref="I24:J24"/>
-    <mergeCell ref="I25:J25"/>
-    <mergeCell ref="I26:J26"/>
-    <mergeCell ref="I27:J27"/>
-    <mergeCell ref="I28:J28"/>
-    <mergeCell ref="H51:J51"/>
-    <mergeCell ref="H52:J52"/>
-    <mergeCell ref="H53:J53"/>
-    <mergeCell ref="H54:J54"/>
-    <mergeCell ref="H55:J55"/>
-    <mergeCell ref="M2:N2"/>
-    <mergeCell ref="I2:L2"/>
-    <mergeCell ref="I4:N4"/>
-    <mergeCell ref="I3:N3"/>
-    <mergeCell ref="I8:J8"/>
-    <mergeCell ref="K8:L8"/>
-    <mergeCell ref="M8:N8"/>
-    <mergeCell ref="X8:Z8"/>
-    <mergeCell ref="X6:Z6"/>
-    <mergeCell ref="I9:L9"/>
-    <mergeCell ref="I10:L10"/>
-    <mergeCell ref="M10:N10"/>
-    <mergeCell ref="I11:L11"/>
-    <mergeCell ref="M11:N11"/>
-    <mergeCell ref="X5:Z5"/>
-    <mergeCell ref="X7:Z7"/>
-    <mergeCell ref="X10:Z10"/>
-    <mergeCell ref="X9:Z9"/>
-    <mergeCell ref="Q8:S8"/>
-    <mergeCell ref="Q9:S9"/>
-    <mergeCell ref="Q10:S10"/>
-    <mergeCell ref="Q11:S11"/>
-    <mergeCell ref="O19:R19"/>
-    <mergeCell ref="H39:J39"/>
-    <mergeCell ref="H40:J40"/>
-    <mergeCell ref="H41:J41"/>
-    <mergeCell ref="H42:J42"/>
-    <mergeCell ref="H43:J43"/>
-    <mergeCell ref="H47:J47"/>
-    <mergeCell ref="H48:J48"/>
-    <mergeCell ref="H49:J49"/>
-    <mergeCell ref="I36:J36"/>
-    <mergeCell ref="H50:J50"/>
-    <mergeCell ref="H44:J44"/>
-    <mergeCell ref="H45:J45"/>
-    <mergeCell ref="H46:J46"/>
-    <mergeCell ref="F52:G52"/>
-    <mergeCell ref="F53:G53"/>
-    <mergeCell ref="F54:G54"/>
-    <mergeCell ref="F55:G55"/>
-    <mergeCell ref="B38:G38"/>
-    <mergeCell ref="F50:G50"/>
-    <mergeCell ref="F51:G51"/>
-    <mergeCell ref="I29:J29"/>
-    <mergeCell ref="I30:J30"/>
-    <mergeCell ref="F46:G46"/>
-    <mergeCell ref="F47:G47"/>
-    <mergeCell ref="F48:G48"/>
-    <mergeCell ref="F49:G49"/>
-    <mergeCell ref="F41:G41"/>
-    <mergeCell ref="F40:G40"/>
-    <mergeCell ref="F42:G42"/>
-    <mergeCell ref="F43:G43"/>
-    <mergeCell ref="F44:G44"/>
-    <mergeCell ref="F45:G45"/>
-    <mergeCell ref="G36:H36"/>
-    <mergeCell ref="Q12:S12"/>
-    <mergeCell ref="B40:C40"/>
-    <mergeCell ref="Q2:S2"/>
-    <mergeCell ref="Q3:S3"/>
-    <mergeCell ref="Q4:S4"/>
-    <mergeCell ref="Q5:S5"/>
-    <mergeCell ref="Q6:S6"/>
-    <mergeCell ref="Q7:S7"/>
-    <mergeCell ref="X2:Z2"/>
-    <mergeCell ref="X3:Z3"/>
-    <mergeCell ref="X4:Z4"/>
-    <mergeCell ref="I7:J7"/>
-    <mergeCell ref="K7:L7"/>
-    <mergeCell ref="M7:N7"/>
-    <mergeCell ref="M9:N9"/>
-    <mergeCell ref="A15:D15"/>
-    <mergeCell ref="I6:J6"/>
-    <mergeCell ref="K5:L5"/>
-    <mergeCell ref="M5:N5"/>
-    <mergeCell ref="K6:L6"/>
-    <mergeCell ref="M6:N6"/>
-    <mergeCell ref="A14:D14"/>
-    <mergeCell ref="E12:G12"/>
-    <mergeCell ref="A13:D13"/>
+    <mergeCell ref="B61:E61"/>
+    <mergeCell ref="B60:E60"/>
+    <mergeCell ref="B68:E68"/>
     <mergeCell ref="B69:E69"/>
     <mergeCell ref="B59:E59"/>
     <mergeCell ref="B58:E58"/>
@@ -4166,9 +4076,109 @@
     <mergeCell ref="B64:E64"/>
     <mergeCell ref="B63:E63"/>
     <mergeCell ref="B62:E62"/>
-    <mergeCell ref="B61:E61"/>
-    <mergeCell ref="B60:E60"/>
-    <mergeCell ref="B68:E68"/>
+    <mergeCell ref="Q12:S12"/>
+    <mergeCell ref="B40:C40"/>
+    <mergeCell ref="Q2:S2"/>
+    <mergeCell ref="Q3:S3"/>
+    <mergeCell ref="Q4:S4"/>
+    <mergeCell ref="Q5:S5"/>
+    <mergeCell ref="Q6:S6"/>
+    <mergeCell ref="Q7:S7"/>
+    <mergeCell ref="I29:J29"/>
+    <mergeCell ref="I30:J30"/>
+    <mergeCell ref="F46:G46"/>
+    <mergeCell ref="F47:G47"/>
+    <mergeCell ref="F48:G48"/>
+    <mergeCell ref="F49:G49"/>
+    <mergeCell ref="F41:G41"/>
+    <mergeCell ref="F40:G40"/>
+    <mergeCell ref="F42:G42"/>
+    <mergeCell ref="F43:G43"/>
+    <mergeCell ref="F44:G44"/>
+    <mergeCell ref="F45:G45"/>
+    <mergeCell ref="G36:H36"/>
+    <mergeCell ref="AC2:AE2"/>
+    <mergeCell ref="AC3:AE3"/>
+    <mergeCell ref="AC4:AE4"/>
+    <mergeCell ref="I7:J7"/>
+    <mergeCell ref="K7:L7"/>
+    <mergeCell ref="M7:N7"/>
+    <mergeCell ref="M9:N9"/>
+    <mergeCell ref="A15:D15"/>
+    <mergeCell ref="I6:J6"/>
+    <mergeCell ref="K5:L5"/>
+    <mergeCell ref="M5:N5"/>
+    <mergeCell ref="K6:L6"/>
+    <mergeCell ref="M6:N6"/>
+    <mergeCell ref="A14:D14"/>
+    <mergeCell ref="E12:G12"/>
+    <mergeCell ref="A13:D13"/>
+    <mergeCell ref="M2:N2"/>
+    <mergeCell ref="I2:L2"/>
+    <mergeCell ref="I4:N4"/>
+    <mergeCell ref="I3:N3"/>
+    <mergeCell ref="F54:G54"/>
+    <mergeCell ref="F55:G55"/>
+    <mergeCell ref="B38:G38"/>
+    <mergeCell ref="F50:G50"/>
+    <mergeCell ref="F51:G51"/>
+    <mergeCell ref="H39:J39"/>
+    <mergeCell ref="H40:J40"/>
+    <mergeCell ref="H41:J41"/>
+    <mergeCell ref="H42:J42"/>
+    <mergeCell ref="H43:J43"/>
+    <mergeCell ref="H47:J47"/>
+    <mergeCell ref="H48:J48"/>
+    <mergeCell ref="H49:J49"/>
+    <mergeCell ref="S19:V19"/>
+    <mergeCell ref="W19:Z19"/>
+    <mergeCell ref="O19:R19"/>
+    <mergeCell ref="H50:J50"/>
+    <mergeCell ref="H44:J44"/>
+    <mergeCell ref="H45:J45"/>
+    <mergeCell ref="H46:J46"/>
+    <mergeCell ref="F52:G52"/>
+    <mergeCell ref="F53:G53"/>
+    <mergeCell ref="I9:L9"/>
+    <mergeCell ref="I10:L10"/>
+    <mergeCell ref="M10:N10"/>
+    <mergeCell ref="I11:L11"/>
+    <mergeCell ref="M11:N11"/>
+    <mergeCell ref="AC5:AE5"/>
+    <mergeCell ref="AC7:AE7"/>
+    <mergeCell ref="AC10:AE10"/>
+    <mergeCell ref="AC9:AE9"/>
+    <mergeCell ref="Q8:S8"/>
+    <mergeCell ref="Q9:S9"/>
+    <mergeCell ref="Q10:S10"/>
+    <mergeCell ref="Q11:S11"/>
+    <mergeCell ref="I8:J8"/>
+    <mergeCell ref="K8:L8"/>
+    <mergeCell ref="M8:N8"/>
+    <mergeCell ref="AC8:AE8"/>
+    <mergeCell ref="AC6:AE6"/>
+    <mergeCell ref="L56:M56"/>
+    <mergeCell ref="I31:J31"/>
+    <mergeCell ref="I32:J32"/>
+    <mergeCell ref="I33:J33"/>
+    <mergeCell ref="I34:J34"/>
+    <mergeCell ref="I35:J35"/>
+    <mergeCell ref="K19:N19"/>
+    <mergeCell ref="I20:J20"/>
+    <mergeCell ref="I21:J21"/>
+    <mergeCell ref="I22:J22"/>
+    <mergeCell ref="I23:J23"/>
+    <mergeCell ref="I24:J24"/>
+    <mergeCell ref="I25:J25"/>
+    <mergeCell ref="I26:J26"/>
+    <mergeCell ref="I27:J27"/>
+    <mergeCell ref="I28:J28"/>
+    <mergeCell ref="H51:J51"/>
+    <mergeCell ref="H52:J52"/>
+    <mergeCell ref="H53:J53"/>
+    <mergeCell ref="H54:J54"/>
+    <mergeCell ref="H55:J55"/>
+    <mergeCell ref="I36:J36"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
